--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19848" uniqueCount="1349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19845" uniqueCount="1349">
   <si>
     <t>DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH</t>
   </si>
@@ -28783,14 +28783,14 @@
       <c r="P197" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="Q197" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R197" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S197" s="3" t="s">
-        <v>46</v>
+      <c r="Q197" s="5">
+        <v>1</v>
+      </c>
+      <c r="R197" s="5">
+        <v>1</v>
+      </c>
+      <c r="S197" s="5">
+        <v>1</v>
       </c>
       <c r="T197" s="3" t="s">
         <v>46</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -80909,13 +80909,13 @@
         <v>79</v>
       </c>
       <c r="Q614" s="5">
+        <v>27</v>
+      </c>
+      <c r="R614" s="5">
         <v>26</v>
       </c>
-      <c r="R614" s="5">
-        <v>25</v>
-      </c>
       <c r="S614" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T614" s="3" t="s">
         <v>1172</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20273" uniqueCount="1384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20240" uniqueCount="1384">
   <si>
     <t>DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH</t>
   </si>
@@ -3583,6 +3583,15 @@
     <t>MSC_BEV_Chương trình Tích Lũy_Trà Búp Non Tea 365_Kênh GT_HCM_All2026_T10</t>
   </si>
   <si>
+    <t>2117565</t>
+  </si>
+  <si>
+    <t>Bé Tư</t>
+  </si>
+  <si>
+    <t>1039, Phạm Văn Đồng</t>
+  </si>
+  <si>
     <t>2800</t>
   </si>
   <si>
@@ -3592,6 +3601,75 @@
     <t>18/27, Đại Học</t>
   </si>
   <si>
+    <t>3057973</t>
+  </si>
+  <si>
+    <t>Hùng Anh</t>
+  </si>
+  <si>
+    <t>23, Đường 100</t>
+  </si>
+  <si>
+    <t>3142121</t>
+  </si>
+  <si>
+    <t>Anh Đại</t>
+  </si>
+  <si>
+    <t>5355</t>
+  </si>
+  <si>
+    <t>Chị Minh</t>
+  </si>
+  <si>
+    <t>57, Chợ Phước Long</t>
+  </si>
+  <si>
+    <t>99924350</t>
+  </si>
+  <si>
+    <t>Cửa Hàng Tiện Lợi</t>
+  </si>
+  <si>
+    <t>ĐH KHXHNV, KP6 , Làng Đại Học</t>
+  </si>
+  <si>
+    <t>Đạt</t>
+  </si>
+  <si>
+    <t>POSM</t>
+  </si>
+  <si>
+    <t>97KM04228</t>
+  </si>
+  <si>
+    <t>Thùng nhựa trong có bánh xe 30L (527x372x270)mm</t>
+  </si>
+  <si>
+    <t>Cai</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>999745910</t>
+  </si>
+  <si>
+    <t>Nhà Ăn Đại Học Quốc Tế</t>
+  </si>
+  <si>
+    <t>Lầu 2 toà A1, Đại Học Quốc Tế</t>
+  </si>
+  <si>
+    <t>5028</t>
+  </si>
+  <si>
+    <t>Ngọc Huy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108, Đường 4 Đại Học Nông Lâm </t>
+  </si>
+  <si>
     <t>3057968</t>
   </si>
   <si>
@@ -3601,75 +3679,6 @@
     <t>71, Đình Phong Phú</t>
   </si>
   <si>
-    <t>3057973</t>
-  </si>
-  <si>
-    <t>Hùng Anh</t>
-  </si>
-  <si>
-    <t>23, Đường 100</t>
-  </si>
-  <si>
-    <t>3142121</t>
-  </si>
-  <si>
-    <t>Anh Đại</t>
-  </si>
-  <si>
-    <t>2117565</t>
-  </si>
-  <si>
-    <t>Bé Tư</t>
-  </si>
-  <si>
-    <t>1039, Phạm Văn Đồng</t>
-  </si>
-  <si>
-    <t>5355</t>
-  </si>
-  <si>
-    <t>Chị Minh</t>
-  </si>
-  <si>
-    <t>57, Chợ Phước Long</t>
-  </si>
-  <si>
-    <t>99924350</t>
-  </si>
-  <si>
-    <t>Cửa Hàng Tiện Lợi</t>
-  </si>
-  <si>
-    <t>ĐH KHXHNV, KP6 , Làng Đại Học</t>
-  </si>
-  <si>
-    <t>Đạt</t>
-  </si>
-  <si>
-    <t>POSM</t>
-  </si>
-  <si>
-    <t>97KM04228</t>
-  </si>
-  <si>
-    <t>Thùng nhựa trong có bánh xe 30L (527x372x270)mm</t>
-  </si>
-  <si>
-    <t>Cai</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>999745910</t>
-  </si>
-  <si>
-    <t>Nhà Ăn Đại Học Quốc Tế</t>
-  </si>
-  <si>
-    <t>Lầu 2 toà A1, Đại Học Quốc Tế</t>
-  </si>
-  <si>
     <t>2340641</t>
   </si>
   <si>
@@ -3677,15 +3686,6 @@
   </si>
   <si>
     <t>89/1/9C, Đường 8</t>
-  </si>
-  <si>
-    <t>5028</t>
-  </si>
-  <si>
-    <t>Ngọc Huy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108, Đường 4 Đại Học Nông Lâm </t>
   </si>
   <si>
     <t>1-6JP933U</t>
@@ -7263,14 +7263,14 @@
       <c r="P24" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>46</v>
+      <c r="Q24" s="5">
+        <v>1</v>
+      </c>
+      <c r="R24" s="5">
+        <v>1</v>
+      </c>
+      <c r="S24" s="5">
+        <v>1</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>46</v>
@@ -12013,14 +12013,14 @@
       <c r="P62" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>46</v>
+      <c r="Q62" s="5">
+        <v>1</v>
+      </c>
+      <c r="R62" s="5">
+        <v>1</v>
+      </c>
+      <c r="S62" s="5">
+        <v>1</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>46</v>
@@ -14138,14 +14138,14 @@
       <c r="P79" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="Q79" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R79" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S79" s="3" t="s">
-        <v>46</v>
+      <c r="Q79" s="5">
+        <v>1</v>
+      </c>
+      <c r="R79" s="5">
+        <v>1</v>
+      </c>
+      <c r="S79" s="5">
+        <v>1</v>
       </c>
       <c r="T79" s="3" t="s">
         <v>46</v>
@@ -15763,14 +15763,14 @@
       <c r="P92" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="Q92" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R92" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S92" s="3" t="s">
-        <v>46</v>
+      <c r="Q92" s="5">
+        <v>1</v>
+      </c>
+      <c r="R92" s="5">
+        <v>1</v>
+      </c>
+      <c r="S92" s="5">
+        <v>1</v>
       </c>
       <c r="T92" s="3" t="s">
         <v>46</v>
@@ -16138,14 +16138,14 @@
       <c r="P95" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="Q95" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R95" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S95" s="3" t="s">
-        <v>46</v>
+      <c r="Q95" s="5">
+        <v>1</v>
+      </c>
+      <c r="R95" s="5">
+        <v>1</v>
+      </c>
+      <c r="S95" s="5">
+        <v>1</v>
       </c>
       <c r="T95" s="3" t="s">
         <v>46</v>
@@ -27263,14 +27263,14 @@
       <c r="P184" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="Q184" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R184" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S184" s="3" t="s">
-        <v>46</v>
+      <c r="Q184" s="5">
+        <v>1</v>
+      </c>
+      <c r="R184" s="5">
+        <v>1</v>
+      </c>
+      <c r="S184" s="5">
+        <v>1</v>
       </c>
       <c r="T184" s="3" t="s">
         <v>46</v>
@@ -44388,14 +44388,14 @@
       <c r="P321" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="Q321" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R321" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S321" s="3" t="s">
-        <v>46</v>
+      <c r="Q321" s="5">
+        <v>1</v>
+      </c>
+      <c r="R321" s="5">
+        <v>1</v>
+      </c>
+      <c r="S321" s="5">
+        <v>1</v>
       </c>
       <c r="T321" s="3" t="s">
         <v>46</v>
@@ -48013,14 +48013,14 @@
       <c r="P350" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="Q350" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R350" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S350" s="3" t="s">
-        <v>46</v>
+      <c r="Q350" s="5">
+        <v>1</v>
+      </c>
+      <c r="R350" s="5">
+        <v>1</v>
+      </c>
+      <c r="S350" s="5">
+        <v>1</v>
       </c>
       <c r="T350" s="3" t="s">
         <v>46</v>
@@ -50889,13 +50889,13 @@
         <v>150</v>
       </c>
       <c r="Q373" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R373" s="5">
         <v>1</v>
       </c>
       <c r="S373" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T373" s="3" t="s">
         <v>46</v>
@@ -62615,28 +62615,28 @@
         <v>46</v>
       </c>
       <c r="I467" s="3" t="s">
-        <v>269</v>
+        <v>1190</v>
       </c>
       <c r="J467" s="3" t="s">
-        <v>270</v>
+        <v>1191</v>
       </c>
       <c r="K467" s="3" t="s">
-        <v>271</v>
+        <v>1192</v>
       </c>
       <c r="L467" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M467" s="3" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="N467" s="3" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="O467" s="3" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="P467" s="3" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="Q467" s="3" t="s">
         <v>46</v>
@@ -62740,28 +62740,28 @@
         <v>46</v>
       </c>
       <c r="I468" s="3" t="s">
-        <v>340</v>
+        <v>184</v>
       </c>
       <c r="J468" s="3" t="s">
-        <v>341</v>
+        <v>185</v>
       </c>
       <c r="K468" s="3" t="s">
-        <v>342</v>
+        <v>186</v>
       </c>
       <c r="L468" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M468" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="N468" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O468" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="P468" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="Q468" s="3" t="s">
         <v>46</v>
@@ -62824,7 +62824,7 @@
         <v>58</v>
       </c>
       <c r="AK468" s="6">
-        <v>46307.90555991898</v>
+        <v>46311.33051195602</v>
       </c>
       <c r="AL468" s="3" t="s">
         <v>46</v>
@@ -62836,7 +62836,7 @@
         <v>58</v>
       </c>
       <c r="AO468" s="6">
-        <v>46307.90555991898</v>
+        <v>46311.33051195602</v>
       </c>
     </row>
     <row r="469" spans="1:41" x14ac:dyDescent="0.25">
@@ -62865,28 +62865,28 @@
         <v>46</v>
       </c>
       <c r="I469" s="3" t="s">
-        <v>1190</v>
+        <v>269</v>
       </c>
       <c r="J469" s="3" t="s">
-        <v>1191</v>
+        <v>270</v>
       </c>
       <c r="K469" s="3" t="s">
-        <v>1192</v>
+        <v>271</v>
       </c>
       <c r="L469" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M469" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="N469" s="3" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="O469" s="3" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="P469" s="3" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="Q469" s="3" t="s">
         <v>46</v>
@@ -62990,28 +62990,28 @@
         <v>46</v>
       </c>
       <c r="I470" s="3" t="s">
-        <v>1193</v>
+        <v>340</v>
       </c>
       <c r="J470" s="3" t="s">
-        <v>1194</v>
+        <v>341</v>
       </c>
       <c r="K470" s="3" t="s">
-        <v>1195</v>
+        <v>342</v>
       </c>
       <c r="L470" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M470" s="3" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="N470" s="3" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="O470" s="3" t="s">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="P470" s="3" t="s">
-        <v>196</v>
+        <v>79</v>
       </c>
       <c r="Q470" s="3" t="s">
         <v>46</v>
@@ -63115,28 +63115,28 @@
         <v>46</v>
       </c>
       <c r="I471" s="3" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="J471" s="3" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="K471" s="3" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="L471" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M471" s="3" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="N471" s="3" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="O471" s="3" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="P471" s="3" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="Q471" s="3" t="s">
         <v>46</v>
@@ -63199,7 +63199,7 @@
         <v>58</v>
       </c>
       <c r="AK471" s="6">
-        <v>46324.30341940973</v>
+        <v>46301.91933796296</v>
       </c>
       <c r="AL471" s="3" t="s">
         <v>46</v>
@@ -63211,7 +63211,7 @@
         <v>58</v>
       </c>
       <c r="AO471" s="6">
-        <v>46324.30341940973</v>
+        <v>46301.91933796296</v>
       </c>
     </row>
     <row r="472" spans="1:41" x14ac:dyDescent="0.25">
@@ -63240,28 +63240,28 @@
         <v>46</v>
       </c>
       <c r="I472" s="3" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="J472" s="3" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="K472" s="3" t="s">
-        <v>104</v>
+        <v>1198</v>
       </c>
       <c r="L472" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M472" s="3" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="N472" s="3" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="O472" s="3" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="P472" s="3" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="Q472" s="3" t="s">
         <v>46</v>
@@ -63324,7 +63324,7 @@
         <v>58</v>
       </c>
       <c r="AK472" s="6">
-        <v>46301.91933796296</v>
+        <v>46324.30341940973</v>
       </c>
       <c r="AL472" s="3" t="s">
         <v>46</v>
@@ -63336,7 +63336,7 @@
         <v>58</v>
       </c>
       <c r="AO472" s="6">
-        <v>46301.91933796296</v>
+        <v>46324.30341940973</v>
       </c>
     </row>
     <row r="473" spans="1:41" x14ac:dyDescent="0.25">
@@ -63365,28 +63365,28 @@
         <v>46</v>
       </c>
       <c r="I473" s="3" t="s">
-        <v>579</v>
+        <v>1199</v>
       </c>
       <c r="J473" s="3" t="s">
-        <v>580</v>
+        <v>1200</v>
       </c>
       <c r="K473" s="3" t="s">
-        <v>581</v>
+        <v>104</v>
       </c>
       <c r="L473" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M473" s="3" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
       <c r="N473" s="3" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="O473" s="3" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="P473" s="3" t="s">
-        <v>164</v>
+        <v>92</v>
       </c>
       <c r="Q473" s="3" t="s">
         <v>46</v>
@@ -63490,28 +63490,28 @@
         <v>46</v>
       </c>
       <c r="I474" s="3" t="s">
-        <v>1201</v>
+        <v>579</v>
       </c>
       <c r="J474" s="3" t="s">
-        <v>1202</v>
+        <v>580</v>
       </c>
       <c r="K474" s="3" t="s">
-        <v>1203</v>
+        <v>581</v>
       </c>
       <c r="L474" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M474" s="3" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="N474" s="3" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="O474" s="3" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="P474" s="3" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="Q474" s="3" t="s">
         <v>46</v>
@@ -63615,28 +63615,28 @@
         <v>46</v>
       </c>
       <c r="I475" s="3" t="s">
-        <v>184</v>
+        <v>1201</v>
       </c>
       <c r="J475" s="3" t="s">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="K475" s="3" t="s">
-        <v>186</v>
+        <v>1203</v>
       </c>
       <c r="L475" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M475" s="3" t="s">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="N475" s="3" t="s">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="O475" s="3" t="s">
-        <v>91</v>
+        <v>202</v>
       </c>
       <c r="P475" s="3" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="Q475" s="3" t="s">
         <v>46</v>
@@ -63699,7 +63699,7 @@
         <v>58</v>
       </c>
       <c r="AK475" s="6">
-        <v>46311.33051195602</v>
+        <v>46324.30341940973</v>
       </c>
       <c r="AL475" s="3" t="s">
         <v>46</v>
@@ -63711,7 +63711,7 @@
         <v>58</v>
       </c>
       <c r="AO475" s="6">
-        <v>46311.33051195602</v>
+        <v>46324.30341940973</v>
       </c>
     </row>
     <row r="476" spans="1:41" x14ac:dyDescent="0.25">
@@ -63737,7 +63737,7 @@
         <v>45</v>
       </c>
       <c r="H476" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I476" s="3" t="s">
         <v>1204</v>
@@ -63752,16 +63752,16 @@
         <v>50</v>
       </c>
       <c r="M476" s="3" t="s">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="N476" s="3" t="s">
-        <v>201</v>
+        <v>115</v>
       </c>
       <c r="O476" s="3" t="s">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="P476" s="3" t="s">
-        <v>203</v>
+        <v>117</v>
       </c>
       <c r="Q476" s="3" t="s">
         <v>46</v>
@@ -63773,7 +63773,7 @@
         <v>46</v>
       </c>
       <c r="T476" s="3" t="s">
-        <v>46</v>
+        <v>1207</v>
       </c>
       <c r="U476" s="3" t="s">
         <v>46</v>
@@ -63790,41 +63790,41 @@
       <c r="Y476" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z476" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA476" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB476" s="3" t="s">
-        <v>46</v>
+      <c r="Z476" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA476" s="7">
+        <v>11</v>
+      </c>
+      <c r="AB476" s="7">
+        <v>1</v>
       </c>
       <c r="AC476" s="3" t="s">
-        <v>46</v>
+        <v>1208</v>
       </c>
       <c r="AD476" s="3" t="s">
-        <v>46</v>
+        <v>1209</v>
       </c>
       <c r="AE476" s="3" t="s">
-        <v>46</v>
+        <v>1210</v>
       </c>
       <c r="AF476" s="3" t="s">
-        <v>46</v>
+        <v>1211</v>
       </c>
       <c r="AG476" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH476" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI476" s="3" t="s">
-        <v>46</v>
+        <v>1212</v>
+      </c>
+      <c r="AH476" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI476" s="3">
+        <v>0</v>
       </c>
       <c r="AJ476" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK476" s="6">
-        <v>46324.30341940973</v>
+        <v>46316.57381339121</v>
       </c>
       <c r="AL476" s="3" t="s">
         <v>46</v>
@@ -63836,7 +63836,7 @@
         <v>58</v>
       </c>
       <c r="AO476" s="6">
-        <v>46324.30341940973</v>
+        <v>46316.57381339121</v>
       </c>
     </row>
     <row r="477" spans="1:41" x14ac:dyDescent="0.25">
@@ -63865,13 +63865,13 @@
         <v>45</v>
       </c>
       <c r="I477" s="3" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="J477" s="3" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="K477" s="3" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="L477" s="3" t="s">
         <v>50</v>
@@ -63898,7 +63898,7 @@
         <v>46</v>
       </c>
       <c r="T477" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U477" s="3" t="s">
         <v>46</v>
@@ -63919,25 +63919,25 @@
         <v>10</v>
       </c>
       <c r="AA477" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB477" s="7">
         <v>1</v>
       </c>
       <c r="AC477" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="AD477" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AE477" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AF477" s="3" t="s">
         <v>1211</v>
       </c>
-      <c r="AD477" s="3" t="s">
+      <c r="AG477" s="3" t="s">
         <v>1212</v>
-      </c>
-      <c r="AE477" s="3" t="s">
-        <v>1213</v>
-      </c>
-      <c r="AF477" s="3" t="s">
-        <v>1214</v>
-      </c>
-      <c r="AG477" s="3" t="s">
-        <v>1215</v>
       </c>
       <c r="AH477" s="7">
         <v>1</v>
@@ -63949,7 +63949,7 @@
         <v>58</v>
       </c>
       <c r="AK477" s="6">
-        <v>46316.57381339121</v>
+        <v>46303.59298695602</v>
       </c>
       <c r="AL477" s="3" t="s">
         <v>46</v>
@@ -63961,7 +63961,7 @@
         <v>58</v>
       </c>
       <c r="AO477" s="6">
-        <v>46316.57381339121</v>
+        <v>46303.59298695602</v>
       </c>
     </row>
     <row r="478" spans="1:41" x14ac:dyDescent="0.25">
@@ -64023,7 +64023,7 @@
         <v>46</v>
       </c>
       <c r="T478" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U478" s="3" t="s">
         <v>46</v>
@@ -64050,19 +64050,19 @@
         <v>1</v>
       </c>
       <c r="AC478" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="AD478" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AE478" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AF478" s="3" t="s">
         <v>1211</v>
       </c>
-      <c r="AD478" s="3" t="s">
+      <c r="AG478" s="3" t="s">
         <v>1212</v>
-      </c>
-      <c r="AE478" s="3" t="s">
-        <v>1213</v>
-      </c>
-      <c r="AF478" s="3" t="s">
-        <v>1214</v>
-      </c>
-      <c r="AG478" s="3" t="s">
-        <v>1215</v>
       </c>
       <c r="AH478" s="7">
         <v>1</v>
@@ -64074,7 +64074,7 @@
         <v>58</v>
       </c>
       <c r="AK478" s="6">
-        <v>46303.59298695602</v>
+        <v>46300.730373495375</v>
       </c>
       <c r="AL478" s="3" t="s">
         <v>46</v>
@@ -64086,7 +64086,7 @@
         <v>58</v>
       </c>
       <c r="AO478" s="6">
-        <v>46303.59298695602</v>
+        <v>46300.730373495375</v>
       </c>
     </row>
     <row r="479" spans="1:41" x14ac:dyDescent="0.25">
@@ -64148,7 +64148,7 @@
         <v>46</v>
       </c>
       <c r="T479" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U479" s="3" t="s">
         <v>46</v>
@@ -64169,28 +64169,28 @@
         <v>10</v>
       </c>
       <c r="AA479" s="7">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AB479" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC479" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="AD479" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AE479" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AF479" s="3" t="s">
         <v>1211</v>
       </c>
-      <c r="AD479" s="3" t="s">
+      <c r="AG479" s="3" t="s">
         <v>1212</v>
       </c>
-      <c r="AE479" s="3" t="s">
-        <v>1213</v>
-      </c>
-      <c r="AF479" s="3" t="s">
-        <v>1214</v>
-      </c>
-      <c r="AG479" s="3" t="s">
-        <v>1215</v>
-      </c>
       <c r="AH479" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI479" s="3">
         <v>0</v>
@@ -64199,7 +64199,7 @@
         <v>58</v>
       </c>
       <c r="AK479" s="6">
-        <v>46301.91933796296</v>
+        <v>46307.90555991898</v>
       </c>
       <c r="AL479" s="3" t="s">
         <v>46</v>
@@ -64211,7 +64211,7 @@
         <v>58</v>
       </c>
       <c r="AO479" s="6">
-        <v>46301.91933796296</v>
+        <v>46307.90555991898</v>
       </c>
     </row>
     <row r="480" spans="1:41" x14ac:dyDescent="0.25">
@@ -64240,28 +64240,28 @@
         <v>45</v>
       </c>
       <c r="I480" s="3" t="s">
-        <v>233</v>
+        <v>1222</v>
       </c>
       <c r="J480" s="3" t="s">
-        <v>234</v>
+        <v>1223</v>
       </c>
       <c r="K480" s="3" t="s">
-        <v>235</v>
+        <v>1224</v>
       </c>
       <c r="L480" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M480" s="3" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="N480" s="3" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="O480" s="3" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="P480" s="3" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="Q480" s="3" t="s">
         <v>46</v>
@@ -64273,7 +64273,7 @@
         <v>46</v>
       </c>
       <c r="T480" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U480" s="3" t="s">
         <v>46</v>
@@ -64294,28 +64294,28 @@
         <v>10</v>
       </c>
       <c r="AA480" s="7">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="AB480" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC480" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="AD480" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AE480" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AF480" s="3" t="s">
         <v>1211</v>
       </c>
-      <c r="AD480" s="3" t="s">
+      <c r="AG480" s="3" t="s">
         <v>1212</v>
       </c>
-      <c r="AE480" s="3" t="s">
-        <v>1213</v>
-      </c>
-      <c r="AF480" s="3" t="s">
-        <v>1214</v>
-      </c>
-      <c r="AG480" s="3" t="s">
-        <v>1215</v>
-      </c>
       <c r="AH480" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI480" s="3">
         <v>0</v>
@@ -64365,28 +64365,28 @@
         <v>45</v>
       </c>
       <c r="I481" s="3" t="s">
-        <v>1222</v>
+        <v>233</v>
       </c>
       <c r="J481" s="3" t="s">
-        <v>1223</v>
+        <v>234</v>
       </c>
       <c r="K481" s="3" t="s">
-        <v>1224</v>
+        <v>235</v>
       </c>
       <c r="L481" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M481" s="3" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="N481" s="3" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="O481" s="3" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="P481" s="3" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="Q481" s="3" t="s">
         <v>46</v>
@@ -64398,7 +64398,7 @@
         <v>46</v>
       </c>
       <c r="T481" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U481" s="3" t="s">
         <v>46</v>
@@ -64419,25 +64419,25 @@
         <v>10</v>
       </c>
       <c r="AA481" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AB481" s="7">
         <v>1</v>
       </c>
       <c r="AC481" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="AD481" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AE481" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AF481" s="3" t="s">
         <v>1211</v>
       </c>
-      <c r="AD481" s="3" t="s">
+      <c r="AG481" s="3" t="s">
         <v>1212</v>
-      </c>
-      <c r="AE481" s="3" t="s">
-        <v>1213</v>
-      </c>
-      <c r="AF481" s="3" t="s">
-        <v>1214</v>
-      </c>
-      <c r="AG481" s="3" t="s">
-        <v>1215</v>
       </c>
       <c r="AH481" s="7">
         <v>1</v>
@@ -64449,7 +64449,7 @@
         <v>58</v>
       </c>
       <c r="AK481" s="6">
-        <v>46300.730373495375</v>
+        <v>46301.91933796296</v>
       </c>
       <c r="AL481" s="3" t="s">
         <v>46</v>
@@ -64461,7 +64461,7 @@
         <v>58</v>
       </c>
       <c r="AO481" s="6">
-        <v>46300.730373495375</v>
+        <v>46301.91933796296</v>
       </c>
     </row>
     <row r="482" spans="1:41" x14ac:dyDescent="0.25">
@@ -64523,7 +64523,7 @@
         <v>9</v>
       </c>
       <c r="T482" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U482" s="3" t="s">
         <v>46</v>
@@ -64550,7 +64550,7 @@
         <v>31</v>
       </c>
       <c r="AC482" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD482" s="3" t="s">
         <v>1229</v>
@@ -64559,10 +64559,10 @@
         <v>1230</v>
       </c>
       <c r="AF482" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG482" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH482" s="7">
         <v>12400000</v>
@@ -64648,7 +64648,7 @@
         <v>3</v>
       </c>
       <c r="T483" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U483" s="3" t="s">
         <v>46</v>
@@ -64675,7 +64675,7 @@
         <v>31</v>
       </c>
       <c r="AC483" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD483" s="3" t="s">
         <v>1229</v>
@@ -64684,10 +64684,10 @@
         <v>1230</v>
       </c>
       <c r="AF483" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG483" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH483" s="7">
         <v>12400000</v>
@@ -64764,16 +64764,16 @@
         <v>65</v>
       </c>
       <c r="Q484" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R484" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S484" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T484" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U484" s="3" t="s">
         <v>46</v>
@@ -64794,13 +64794,13 @@
         <v>46</v>
       </c>
       <c r="AA484" s="7">
-        <v>756566</v>
+        <v>1147670</v>
       </c>
       <c r="AB484" s="7">
         <v>31</v>
       </c>
       <c r="AC484" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD484" s="3" t="s">
         <v>1229</v>
@@ -64809,10 +64809,10 @@
         <v>1230</v>
       </c>
       <c r="AF484" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG484" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH484" s="7">
         <v>12400000</v>
@@ -64889,16 +64889,16 @@
         <v>210</v>
       </c>
       <c r="Q485" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R485" s="3">
         <v>0</v>
       </c>
       <c r="S485" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T485" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U485" s="3" t="s">
         <v>46</v>
@@ -64925,7 +64925,7 @@
         <v>31</v>
       </c>
       <c r="AC485" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD485" s="3" t="s">
         <v>1229</v>
@@ -64934,10 +64934,10 @@
         <v>1230</v>
       </c>
       <c r="AF485" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG485" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH485" s="7">
         <v>12400000</v>
@@ -65023,7 +65023,7 @@
         <v>10</v>
       </c>
       <c r="T486" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U486" s="3" t="s">
         <v>46</v>
@@ -65050,7 +65050,7 @@
         <v>31</v>
       </c>
       <c r="AC486" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD486" s="3" t="s">
         <v>1229</v>
@@ -65059,10 +65059,10 @@
         <v>1230</v>
       </c>
       <c r="AF486" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG486" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH486" s="7">
         <v>12400000</v>
@@ -65139,16 +65139,16 @@
         <v>196</v>
       </c>
       <c r="Q487" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R487" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S487" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T487" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U487" s="3" t="s">
         <v>46</v>
@@ -65175,7 +65175,7 @@
         <v>31</v>
       </c>
       <c r="AC487" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD487" s="3" t="s">
         <v>1229</v>
@@ -65184,10 +65184,10 @@
         <v>1230</v>
       </c>
       <c r="AF487" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG487" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH487" s="7">
         <v>12400000</v>
@@ -65264,16 +65264,16 @@
         <v>164</v>
       </c>
       <c r="Q488" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R488" s="5">
         <v>7</v>
       </c>
       <c r="S488" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T488" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U488" s="3" t="s">
         <v>46</v>
@@ -65300,7 +65300,7 @@
         <v>31</v>
       </c>
       <c r="AC488" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD488" s="3" t="s">
         <v>1229</v>
@@ -65309,10 +65309,10 @@
         <v>1230</v>
       </c>
       <c r="AF488" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG488" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH488" s="7">
         <v>12400000</v>
@@ -65398,7 +65398,7 @@
         <v>7</v>
       </c>
       <c r="T489" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U489" s="3" t="s">
         <v>46</v>
@@ -65425,7 +65425,7 @@
         <v>31</v>
       </c>
       <c r="AC489" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD489" s="3" t="s">
         <v>1229</v>
@@ -65434,10 +65434,10 @@
         <v>1230</v>
       </c>
       <c r="AF489" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG489" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH489" s="7">
         <v>12400000</v>
@@ -65523,7 +65523,7 @@
         <v>3</v>
       </c>
       <c r="T490" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U490" s="3" t="s">
         <v>46</v>
@@ -65550,7 +65550,7 @@
         <v>31</v>
       </c>
       <c r="AC490" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD490" s="3" t="s">
         <v>1229</v>
@@ -65559,10 +65559,10 @@
         <v>1230</v>
       </c>
       <c r="AF490" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG490" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH490" s="7">
         <v>12400000</v>
@@ -65639,16 +65639,16 @@
         <v>150</v>
       </c>
       <c r="Q491" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R491" s="3">
         <v>0</v>
       </c>
       <c r="S491" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T491" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U491" s="3" t="s">
         <v>46</v>
@@ -65675,7 +65675,7 @@
         <v>31</v>
       </c>
       <c r="AC491" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD491" s="3" t="s">
         <v>1229</v>
@@ -65684,10 +65684,10 @@
         <v>1230</v>
       </c>
       <c r="AF491" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG491" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH491" s="7">
         <v>12400000</v>
@@ -65764,16 +65764,16 @@
         <v>54</v>
       </c>
       <c r="Q492" s="5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R492" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S492" s="5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T492" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U492" s="3" t="s">
         <v>46</v>
@@ -65800,7 +65800,7 @@
         <v>31</v>
       </c>
       <c r="AC492" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD492" s="3" t="s">
         <v>1229</v>
@@ -65809,10 +65809,10 @@
         <v>1230</v>
       </c>
       <c r="AF492" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG492" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH492" s="7">
         <v>12400000</v>
@@ -65889,16 +65889,16 @@
         <v>65</v>
       </c>
       <c r="Q493" s="5">
+        <v>19</v>
+      </c>
+      <c r="R493" s="5">
         <v>18</v>
       </c>
-      <c r="R493" s="5">
-        <v>17</v>
-      </c>
       <c r="S493" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T493" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U493" s="3" t="s">
         <v>46</v>
@@ -65925,7 +65925,7 @@
         <v>31</v>
       </c>
       <c r="AC493" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD493" s="3" t="s">
         <v>1229</v>
@@ -65934,10 +65934,10 @@
         <v>1230</v>
       </c>
       <c r="AF493" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG493" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH493" s="7">
         <v>12400000</v>
@@ -66014,16 +66014,16 @@
         <v>164</v>
       </c>
       <c r="Q494" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R494" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S494" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T494" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U494" s="3" t="s">
         <v>46</v>
@@ -66044,13 +66044,13 @@
         <v>46</v>
       </c>
       <c r="AA494" s="7">
-        <v>10778468</v>
+        <v>18082468</v>
       </c>
       <c r="AB494" s="7">
         <v>31</v>
       </c>
       <c r="AC494" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD494" s="3" t="s">
         <v>1229</v>
@@ -66059,10 +66059,10 @@
         <v>1230</v>
       </c>
       <c r="AF494" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG494" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH494" s="7">
         <v>12400000</v>
@@ -66139,16 +66139,16 @@
         <v>232</v>
       </c>
       <c r="Q495" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R495" s="3">
         <v>0</v>
       </c>
       <c r="S495" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T495" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U495" s="3" t="s">
         <v>46</v>
@@ -66175,7 +66175,7 @@
         <v>31</v>
       </c>
       <c r="AC495" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD495" s="3" t="s">
         <v>1229</v>
@@ -66184,10 +66184,10 @@
         <v>1230</v>
       </c>
       <c r="AF495" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG495" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH495" s="7">
         <v>12400000</v>
@@ -66264,16 +66264,16 @@
         <v>65</v>
       </c>
       <c r="Q496" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R496" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S496" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T496" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U496" s="3" t="s">
         <v>46</v>
@@ -66294,13 +66294,13 @@
         <v>46</v>
       </c>
       <c r="AA496" s="7">
-        <v>7429100</v>
+        <v>7870700</v>
       </c>
       <c r="AB496" s="7">
         <v>31</v>
       </c>
       <c r="AC496" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD496" s="3" t="s">
         <v>1229</v>
@@ -66309,10 +66309,10 @@
         <v>1230</v>
       </c>
       <c r="AF496" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG496" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH496" s="7">
         <v>12400000</v>
@@ -66389,16 +66389,16 @@
         <v>79</v>
       </c>
       <c r="Q497" s="5">
+        <v>25</v>
+      </c>
+      <c r="R497" s="5">
         <v>24</v>
       </c>
-      <c r="R497" s="5">
-        <v>23</v>
-      </c>
       <c r="S497" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T497" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U497" s="3" t="s">
         <v>46</v>
@@ -66419,13 +66419,13 @@
         <v>46</v>
       </c>
       <c r="AA497" s="7">
-        <v>1381264</v>
+        <v>2196976</v>
       </c>
       <c r="AB497" s="7">
         <v>31</v>
       </c>
       <c r="AC497" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD497" s="3" t="s">
         <v>1229</v>
@@ -66434,10 +66434,10 @@
         <v>1230</v>
       </c>
       <c r="AF497" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG497" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH497" s="7">
         <v>12400000</v>
@@ -66514,16 +66514,16 @@
         <v>164</v>
       </c>
       <c r="Q498" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R498" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S498" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T498" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U498" s="3" t="s">
         <v>46</v>
@@ -66550,7 +66550,7 @@
         <v>31</v>
       </c>
       <c r="AC498" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD498" s="3" t="s">
         <v>1229</v>
@@ -66559,10 +66559,10 @@
         <v>1230</v>
       </c>
       <c r="AF498" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG498" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH498" s="7">
         <v>12400000</v>
@@ -66639,16 +66639,16 @@
         <v>140</v>
       </c>
       <c r="Q499" s="5">
+        <v>14</v>
+      </c>
+      <c r="R499" s="5">
         <v>12</v>
       </c>
-      <c r="R499" s="5">
-        <v>10</v>
-      </c>
       <c r="S499" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T499" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U499" s="3" t="s">
         <v>46</v>
@@ -66669,13 +66669,13 @@
         <v>46</v>
       </c>
       <c r="AA499" s="7">
-        <v>15223549</v>
+        <v>16001949</v>
       </c>
       <c r="AB499" s="7">
         <v>31</v>
       </c>
       <c r="AC499" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD499" s="3" t="s">
         <v>1229</v>
@@ -66684,10 +66684,10 @@
         <v>1230</v>
       </c>
       <c r="AF499" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG499" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH499" s="7">
         <v>12400000</v>
@@ -66773,7 +66773,7 @@
         <v>12</v>
       </c>
       <c r="T500" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U500" s="3" t="s">
         <v>46</v>
@@ -66794,13 +66794,13 @@
         <v>46</v>
       </c>
       <c r="AA500" s="7">
-        <v>6722299</v>
+        <v>7722299</v>
       </c>
       <c r="AB500" s="7">
         <v>31</v>
       </c>
       <c r="AC500" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD500" s="3" t="s">
         <v>1229</v>
@@ -66809,10 +66809,10 @@
         <v>1230</v>
       </c>
       <c r="AF500" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG500" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH500" s="7">
         <v>12400000</v>
@@ -66889,16 +66889,16 @@
         <v>196</v>
       </c>
       <c r="Q501" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R501" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S501" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T501" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U501" s="3" t="s">
         <v>46</v>
@@ -66925,7 +66925,7 @@
         <v>31</v>
       </c>
       <c r="AC501" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD501" s="3" t="s">
         <v>1229</v>
@@ -66934,10 +66934,10 @@
         <v>1230</v>
       </c>
       <c r="AF501" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG501" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH501" s="7">
         <v>12400000</v>
@@ -67023,7 +67023,7 @@
         <v>4</v>
       </c>
       <c r="T502" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U502" s="3" t="s">
         <v>46</v>
@@ -67044,13 +67044,13 @@
         <v>46</v>
       </c>
       <c r="AA502" s="7">
-        <v>4362825</v>
+        <v>5510425</v>
       </c>
       <c r="AB502" s="7">
         <v>31</v>
       </c>
       <c r="AC502" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD502" s="3" t="s">
         <v>1229</v>
@@ -67059,10 +67059,10 @@
         <v>1230</v>
       </c>
       <c r="AF502" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG502" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH502" s="7">
         <v>12400000</v>
@@ -67148,7 +67148,7 @@
         <v>2</v>
       </c>
       <c r="T503" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U503" s="3" t="s">
         <v>46</v>
@@ -67169,13 +67169,13 @@
         <v>46</v>
       </c>
       <c r="AA503" s="7">
-        <v>4724303</v>
+        <v>5098703</v>
       </c>
       <c r="AB503" s="7">
         <v>31</v>
       </c>
       <c r="AC503" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD503" s="3" t="s">
         <v>1229</v>
@@ -67184,10 +67184,10 @@
         <v>1230</v>
       </c>
       <c r="AF503" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG503" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH503" s="7">
         <v>12400000</v>
@@ -67273,7 +67273,7 @@
         <v>10</v>
       </c>
       <c r="T504" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U504" s="3" t="s">
         <v>46</v>
@@ -67294,13 +67294,13 @@
         <v>46</v>
       </c>
       <c r="AA504" s="7">
-        <v>1680143</v>
+        <v>1728143</v>
       </c>
       <c r="AB504" s="7">
         <v>31</v>
       </c>
       <c r="AC504" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD504" s="3" t="s">
         <v>1229</v>
@@ -67309,10 +67309,10 @@
         <v>1230</v>
       </c>
       <c r="AF504" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG504" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH504" s="7">
         <v>12400000</v>
@@ -67398,7 +67398,7 @@
         <v>11</v>
       </c>
       <c r="T505" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U505" s="3" t="s">
         <v>46</v>
@@ -67419,13 +67419,13 @@
         <v>46</v>
       </c>
       <c r="AA505" s="7">
-        <v>6578289</v>
+        <v>9672464</v>
       </c>
       <c r="AB505" s="7">
         <v>31</v>
       </c>
       <c r="AC505" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD505" s="3" t="s">
         <v>1229</v>
@@ -67434,10 +67434,10 @@
         <v>1230</v>
       </c>
       <c r="AF505" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG505" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH505" s="7">
         <v>12400000</v>
@@ -67523,7 +67523,7 @@
         <v>5</v>
       </c>
       <c r="T506" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U506" s="3" t="s">
         <v>46</v>
@@ -67550,7 +67550,7 @@
         <v>31</v>
       </c>
       <c r="AC506" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD506" s="3" t="s">
         <v>1229</v>
@@ -67559,10 +67559,10 @@
         <v>1230</v>
       </c>
       <c r="AF506" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG506" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH506" s="7">
         <v>12400000</v>
@@ -67648,7 +67648,7 @@
         <v>25</v>
       </c>
       <c r="T507" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U507" s="3" t="s">
         <v>46</v>
@@ -67675,7 +67675,7 @@
         <v>31</v>
       </c>
       <c r="AC507" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD507" s="3" t="s">
         <v>1229</v>
@@ -67684,10 +67684,10 @@
         <v>1230</v>
       </c>
       <c r="AF507" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG507" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH507" s="7">
         <v>12400000</v>
@@ -67773,7 +67773,7 @@
         <v>6</v>
       </c>
       <c r="T508" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U508" s="3" t="s">
         <v>46</v>
@@ -67794,13 +67794,13 @@
         <v>46</v>
       </c>
       <c r="AA508" s="7">
-        <v>863361</v>
+        <v>2324385</v>
       </c>
       <c r="AB508" s="7">
         <v>31</v>
       </c>
       <c r="AC508" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD508" s="3" t="s">
         <v>1229</v>
@@ -67809,10 +67809,10 @@
         <v>1230</v>
       </c>
       <c r="AF508" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG508" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH508" s="7">
         <v>18600000</v>
@@ -67898,7 +67898,7 @@
         <v>9</v>
       </c>
       <c r="T509" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U509" s="3" t="s">
         <v>46</v>
@@ -67925,7 +67925,7 @@
         <v>31</v>
       </c>
       <c r="AC509" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD509" s="3" t="s">
         <v>1229</v>
@@ -67934,10 +67934,10 @@
         <v>1230</v>
       </c>
       <c r="AF509" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG509" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH509" s="7">
         <v>18600000</v>
@@ -68014,16 +68014,16 @@
         <v>164</v>
       </c>
       <c r="Q510" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R510" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S510" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T510" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U510" s="3" t="s">
         <v>46</v>
@@ -68050,7 +68050,7 @@
         <v>31</v>
       </c>
       <c r="AC510" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD510" s="3" t="s">
         <v>1229</v>
@@ -68059,10 +68059,10 @@
         <v>1230</v>
       </c>
       <c r="AF510" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG510" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH510" s="7">
         <v>12400000</v>
@@ -68139,16 +68139,16 @@
         <v>210</v>
       </c>
       <c r="Q511" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R511" s="3">
         <v>0</v>
       </c>
       <c r="S511" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T511" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U511" s="3" t="s">
         <v>46</v>
@@ -68175,7 +68175,7 @@
         <v>31</v>
       </c>
       <c r="AC511" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD511" s="3" t="s">
         <v>1229</v>
@@ -68184,10 +68184,10 @@
         <v>1230</v>
       </c>
       <c r="AF511" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG511" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH511" s="7">
         <v>12400000</v>
@@ -68264,16 +68264,16 @@
         <v>210</v>
       </c>
       <c r="Q512" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R512" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S512" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T512" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U512" s="3" t="s">
         <v>46</v>
@@ -68294,13 +68294,13 @@
         <v>46</v>
       </c>
       <c r="AA512" s="7">
-        <v>104000</v>
+        <v>329000</v>
       </c>
       <c r="AB512" s="7">
         <v>31</v>
       </c>
       <c r="AC512" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD512" s="3" t="s">
         <v>1229</v>
@@ -68309,10 +68309,10 @@
         <v>1230</v>
       </c>
       <c r="AF512" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG512" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH512" s="7">
         <v>12400000</v>
@@ -68398,7 +68398,7 @@
         <v>1</v>
       </c>
       <c r="T513" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U513" s="3" t="s">
         <v>46</v>
@@ -68425,7 +68425,7 @@
         <v>31</v>
       </c>
       <c r="AC513" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD513" s="3" t="s">
         <v>1229</v>
@@ -68434,10 +68434,10 @@
         <v>1230</v>
       </c>
       <c r="AF513" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG513" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH513" s="7">
         <v>12400000</v>
@@ -68514,16 +68514,16 @@
         <v>196</v>
       </c>
       <c r="Q514" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R514" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S514" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T514" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U514" s="3" t="s">
         <v>46</v>
@@ -68550,7 +68550,7 @@
         <v>31</v>
       </c>
       <c r="AC514" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD514" s="3" t="s">
         <v>1229</v>
@@ -68559,10 +68559,10 @@
         <v>1230</v>
       </c>
       <c r="AF514" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG514" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH514" s="7">
         <v>12400000</v>
@@ -68648,7 +68648,7 @@
         <v>2</v>
       </c>
       <c r="T515" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U515" s="3" t="s">
         <v>46</v>
@@ -68675,7 +68675,7 @@
         <v>31</v>
       </c>
       <c r="AC515" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD515" s="3" t="s">
         <v>1229</v>
@@ -68684,10 +68684,10 @@
         <v>1230</v>
       </c>
       <c r="AF515" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG515" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH515" s="7">
         <v>12400000</v>
@@ -68773,7 +68773,7 @@
         <v>13</v>
       </c>
       <c r="T516" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U516" s="3" t="s">
         <v>46</v>
@@ -68794,13 +68794,13 @@
         <v>46</v>
       </c>
       <c r="AA516" s="7">
-        <v>3005000</v>
+        <v>6758528</v>
       </c>
       <c r="AB516" s="7">
         <v>31</v>
       </c>
       <c r="AC516" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD516" s="3" t="s">
         <v>1229</v>
@@ -68809,10 +68809,10 @@
         <v>1230</v>
       </c>
       <c r="AF516" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG516" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH516" s="7">
         <v>12400000</v>
@@ -68898,7 +68898,7 @@
         <v>1</v>
       </c>
       <c r="T517" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U517" s="3" t="s">
         <v>46</v>
@@ -69023,7 +69023,7 @@
         <v>2</v>
       </c>
       <c r="T518" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U518" s="3" t="s">
         <v>46</v>
@@ -69148,7 +69148,7 @@
         <v>46</v>
       </c>
       <c r="T519" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U519" s="3" t="s">
         <v>46</v>
@@ -69273,7 +69273,7 @@
         <v>1</v>
       </c>
       <c r="T520" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U520" s="3" t="s">
         <v>46</v>
@@ -69398,7 +69398,7 @@
         <v>2</v>
       </c>
       <c r="T521" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U521" s="3" t="s">
         <v>46</v>
@@ -69523,7 +69523,7 @@
         <v>3</v>
       </c>
       <c r="T522" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U522" s="3" t="s">
         <v>46</v>
@@ -69648,7 +69648,7 @@
         <v>46</v>
       </c>
       <c r="T523" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U523" s="3" t="s">
         <v>46</v>
@@ -69773,7 +69773,7 @@
         <v>3</v>
       </c>
       <c r="T524" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U524" s="3" t="s">
         <v>46</v>
@@ -69898,7 +69898,7 @@
         <v>1</v>
       </c>
       <c r="T525" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U525" s="3" t="s">
         <v>46</v>
@@ -69919,7 +69919,7 @@
         <v>46</v>
       </c>
       <c r="AA525" s="7">
-        <v>8860825</v>
+        <v>8994825</v>
       </c>
       <c r="AB525" s="7">
         <v>1</v>
@@ -70023,7 +70023,7 @@
         <v>46</v>
       </c>
       <c r="T526" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U526" s="3" t="s">
         <v>46</v>
@@ -70044,7 +70044,7 @@
         <v>46</v>
       </c>
       <c r="AA526" s="7">
-        <v>708999</v>
+        <v>1310679</v>
       </c>
       <c r="AB526" s="7">
         <v>1</v>
@@ -70148,7 +70148,7 @@
         <v>46</v>
       </c>
       <c r="T527" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U527" s="3" t="s">
         <v>46</v>
@@ -70263,17 +70263,17 @@
       <c r="P528" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="Q528" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R528" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S528" s="3" t="s">
-        <v>46</v>
+      <c r="Q528" s="5">
+        <v>1</v>
+      </c>
+      <c r="R528" s="3">
+        <v>0</v>
+      </c>
+      <c r="S528" s="5">
+        <v>1</v>
       </c>
       <c r="T528" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U528" s="3" t="s">
         <v>46</v>
@@ -70294,7 +70294,7 @@
         <v>46</v>
       </c>
       <c r="AA528" s="7">
-        <v>10132848</v>
+        <v>11083248</v>
       </c>
       <c r="AB528" s="7">
         <v>1</v>
@@ -70398,7 +70398,7 @@
         <v>2</v>
       </c>
       <c r="T529" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U529" s="3" t="s">
         <v>46</v>
@@ -70419,7 +70419,7 @@
         <v>46</v>
       </c>
       <c r="AA529" s="7">
-        <v>546791</v>
+        <v>825791</v>
       </c>
       <c r="AB529" s="7">
         <v>1</v>
@@ -70523,7 +70523,7 @@
         <v>3</v>
       </c>
       <c r="T530" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U530" s="3" t="s">
         <v>46</v>
@@ -70648,7 +70648,7 @@
         <v>5</v>
       </c>
       <c r="T531" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U531" s="3" t="s">
         <v>46</v>
@@ -70764,16 +70764,16 @@
         <v>150</v>
       </c>
       <c r="Q532" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R532" s="5">
         <v>1</v>
       </c>
       <c r="S532" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T532" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U532" s="3" t="s">
         <v>46</v>
@@ -70898,7 +70898,7 @@
         <v>4</v>
       </c>
       <c r="T533" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U533" s="3" t="s">
         <v>46</v>
@@ -70919,7 +70919,7 @@
         <v>46</v>
       </c>
       <c r="AA533" s="7">
-        <v>558000</v>
+        <v>942000</v>
       </c>
       <c r="AB533" s="7">
         <v>1</v>
@@ -71023,7 +71023,7 @@
         <v>1</v>
       </c>
       <c r="T534" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U534" s="3" t="s">
         <v>46</v>
@@ -71148,7 +71148,7 @@
         <v>1</v>
       </c>
       <c r="T535" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U535" s="3" t="s">
         <v>46</v>
@@ -71273,7 +71273,7 @@
         <v>5</v>
       </c>
       <c r="T536" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U536" s="3" t="s">
         <v>46</v>
@@ -71398,7 +71398,7 @@
         <v>46</v>
       </c>
       <c r="T537" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U537" s="3" t="s">
         <v>46</v>
@@ -71523,7 +71523,7 @@
         <v>2</v>
       </c>
       <c r="T538" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U538" s="3" t="s">
         <v>46</v>
@@ -71648,7 +71648,7 @@
         <v>1</v>
       </c>
       <c r="T539" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U539" s="3" t="s">
         <v>46</v>
@@ -71669,7 +71669,7 @@
         <v>46</v>
       </c>
       <c r="AA539" s="7">
-        <v>279000</v>
+        <v>413000</v>
       </c>
       <c r="AB539" s="7">
         <v>1</v>
@@ -71773,7 +71773,7 @@
         <v>2</v>
       </c>
       <c r="T540" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U540" s="3" t="s">
         <v>46</v>
@@ -71898,7 +71898,7 @@
         <v>1</v>
       </c>
       <c r="T541" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U541" s="3" t="s">
         <v>46</v>
@@ -71919,7 +71919,7 @@
         <v>46</v>
       </c>
       <c r="AA541" s="7">
-        <v>570240</v>
+        <v>2351880</v>
       </c>
       <c r="AB541" s="7">
         <v>1</v>
@@ -72023,7 +72023,7 @@
         <v>1</v>
       </c>
       <c r="T542" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U542" s="3" t="s">
         <v>46</v>
@@ -72148,7 +72148,7 @@
         <v>3</v>
       </c>
       <c r="T543" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U543" s="3" t="s">
         <v>46</v>
@@ -72273,7 +72273,7 @@
         <v>3</v>
       </c>
       <c r="T544" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U544" s="3" t="s">
         <v>46</v>
@@ -72398,7 +72398,7 @@
         <v>1</v>
       </c>
       <c r="T545" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U545" s="3" t="s">
         <v>46</v>
@@ -72523,7 +72523,7 @@
         <v>3</v>
       </c>
       <c r="T546" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U546" s="3" t="s">
         <v>46</v>
@@ -72544,7 +72544,7 @@
         <v>46</v>
       </c>
       <c r="AA546" s="7">
-        <v>1635706</v>
+        <v>2649996</v>
       </c>
       <c r="AB546" s="7">
         <v>1</v>
@@ -72648,7 +72648,7 @@
         <v>2</v>
       </c>
       <c r="T547" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U547" s="3" t="s">
         <v>46</v>
@@ -72773,7 +72773,7 @@
         <v>1</v>
       </c>
       <c r="T548" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U548" s="3" t="s">
         <v>46</v>
@@ -72898,7 +72898,7 @@
         <v>1</v>
       </c>
       <c r="T549" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U549" s="3" t="s">
         <v>46</v>
@@ -73023,7 +73023,7 @@
         <v>2</v>
       </c>
       <c r="T550" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U550" s="3" t="s">
         <v>46</v>
@@ -73148,7 +73148,7 @@
         <v>46</v>
       </c>
       <c r="T551" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U551" s="3" t="s">
         <v>46</v>
@@ -73273,7 +73273,7 @@
         <v>1</v>
       </c>
       <c r="T552" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U552" s="3" t="s">
         <v>46</v>
@@ -73398,7 +73398,7 @@
         <v>1</v>
       </c>
       <c r="T553" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U553" s="3" t="s">
         <v>46</v>
@@ -73523,7 +73523,7 @@
         <v>46</v>
       </c>
       <c r="T554" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U554" s="3" t="s">
         <v>46</v>
@@ -73648,7 +73648,7 @@
         <v>1</v>
       </c>
       <c r="T555" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U555" s="3" t="s">
         <v>46</v>
@@ -73773,7 +73773,7 @@
         <v>5</v>
       </c>
       <c r="T556" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U556" s="3" t="s">
         <v>46</v>
@@ -73794,13 +73794,13 @@
         <v>46</v>
       </c>
       <c r="AA556" s="7">
-        <v>708999</v>
+        <v>1310679</v>
       </c>
       <c r="AB556" s="7">
         <v>31</v>
       </c>
       <c r="AC556" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD556" s="3" t="s">
         <v>1229</v>
@@ -73809,10 +73809,10 @@
         <v>1230</v>
       </c>
       <c r="AF556" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG556" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH556" s="7">
         <v>6200000</v>
@@ -73889,16 +73889,16 @@
         <v>54</v>
       </c>
       <c r="Q557" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R557" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S557" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T557" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U557" s="3" t="s">
         <v>46</v>
@@ -73925,7 +73925,7 @@
         <v>31</v>
       </c>
       <c r="AC557" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD557" s="3" t="s">
         <v>1229</v>
@@ -73934,10 +73934,10 @@
         <v>1230</v>
       </c>
       <c r="AF557" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG557" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH557" s="7">
         <v>6200000</v>
@@ -74023,7 +74023,7 @@
         <v>1</v>
       </c>
       <c r="T558" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U558" s="3" t="s">
         <v>46</v>
@@ -74050,7 +74050,7 @@
         <v>31</v>
       </c>
       <c r="AC558" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD558" s="3" t="s">
         <v>1229</v>
@@ -74059,10 +74059,10 @@
         <v>1230</v>
       </c>
       <c r="AF558" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG558" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH558" s="7">
         <v>6200000</v>
@@ -74139,16 +74139,16 @@
         <v>196</v>
       </c>
       <c r="Q559" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R559" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S559" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T559" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U559" s="3" t="s">
         <v>46</v>
@@ -74175,7 +74175,7 @@
         <v>31</v>
       </c>
       <c r="AC559" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD559" s="3" t="s">
         <v>1229</v>
@@ -74184,10 +74184,10 @@
         <v>1230</v>
       </c>
       <c r="AF559" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG559" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH559" s="7">
         <v>6200000</v>
@@ -74273,7 +74273,7 @@
         <v>6</v>
       </c>
       <c r="T560" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U560" s="3" t="s">
         <v>46</v>
@@ -74300,7 +74300,7 @@
         <v>31</v>
       </c>
       <c r="AC560" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD560" s="3" t="s">
         <v>1229</v>
@@ -74309,10 +74309,10 @@
         <v>1230</v>
       </c>
       <c r="AF560" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG560" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH560" s="7">
         <v>6200000</v>
@@ -74389,16 +74389,16 @@
         <v>65</v>
       </c>
       <c r="Q561" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R561" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S561" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T561" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U561" s="3" t="s">
         <v>46</v>
@@ -74425,7 +74425,7 @@
         <v>31</v>
       </c>
       <c r="AC561" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD561" s="3" t="s">
         <v>1229</v>
@@ -74434,10 +74434,10 @@
         <v>1230</v>
       </c>
       <c r="AF561" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG561" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH561" s="7">
         <v>6200000</v>
@@ -74523,7 +74523,7 @@
         <v>4</v>
       </c>
       <c r="T562" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U562" s="3" t="s">
         <v>46</v>
@@ -74550,7 +74550,7 @@
         <v>31</v>
       </c>
       <c r="AC562" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD562" s="3" t="s">
         <v>1229</v>
@@ -74559,10 +74559,10 @@
         <v>1230</v>
       </c>
       <c r="AF562" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG562" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH562" s="7">
         <v>6200000</v>
@@ -74639,16 +74639,16 @@
         <v>54</v>
       </c>
       <c r="Q563" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R563" s="5">
         <v>3</v>
       </c>
       <c r="S563" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T563" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U563" s="3" t="s">
         <v>46</v>
@@ -74675,7 +74675,7 @@
         <v>31</v>
       </c>
       <c r="AC563" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD563" s="3" t="s">
         <v>1229</v>
@@ -74684,10 +74684,10 @@
         <v>1230</v>
       </c>
       <c r="AF563" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG563" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH563" s="7">
         <v>6200000</v>
@@ -74764,16 +74764,16 @@
         <v>196</v>
       </c>
       <c r="Q564" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R564" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S564" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T564" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U564" s="3" t="s">
         <v>46</v>
@@ -74800,7 +74800,7 @@
         <v>31</v>
       </c>
       <c r="AC564" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD564" s="3" t="s">
         <v>1229</v>
@@ -74809,10 +74809,10 @@
         <v>1230</v>
       </c>
       <c r="AF564" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG564" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH564" s="7">
         <v>6200000</v>
@@ -74898,7 +74898,7 @@
         <v>10</v>
       </c>
       <c r="T565" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U565" s="3" t="s">
         <v>46</v>
@@ -74919,13 +74919,13 @@
         <v>46</v>
       </c>
       <c r="AA565" s="7">
-        <v>1635706</v>
+        <v>2649996</v>
       </c>
       <c r="AB565" s="7">
         <v>31</v>
       </c>
       <c r="AC565" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD565" s="3" t="s">
         <v>1229</v>
@@ -74934,10 +74934,10 @@
         <v>1230</v>
       </c>
       <c r="AF565" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG565" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH565" s="7">
         <v>6200000</v>
@@ -75023,7 +75023,7 @@
         <v>9</v>
       </c>
       <c r="T566" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U566" s="3" t="s">
         <v>46</v>
@@ -75050,7 +75050,7 @@
         <v>31</v>
       </c>
       <c r="AC566" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD566" s="3" t="s">
         <v>1229</v>
@@ -75059,10 +75059,10 @@
         <v>1230</v>
       </c>
       <c r="AF566" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG566" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH566" s="7">
         <v>6200000</v>
@@ -75148,7 +75148,7 @@
         <v>28</v>
       </c>
       <c r="T567" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U567" s="3" t="s">
         <v>46</v>
@@ -75175,7 +75175,7 @@
         <v>31</v>
       </c>
       <c r="AC567" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD567" s="3" t="s">
         <v>1229</v>
@@ -75184,10 +75184,10 @@
         <v>1230</v>
       </c>
       <c r="AF567" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG567" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH567" s="7">
         <v>6200000</v>
@@ -75264,16 +75264,16 @@
         <v>54</v>
       </c>
       <c r="Q568" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R568" s="5">
         <v>2</v>
       </c>
       <c r="S568" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T568" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U568" s="3" t="s">
         <v>46</v>
@@ -75300,7 +75300,7 @@
         <v>31</v>
       </c>
       <c r="AC568" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD568" s="3" t="s">
         <v>1229</v>
@@ -75309,10 +75309,10 @@
         <v>1230</v>
       </c>
       <c r="AF568" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG568" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH568" s="7">
         <v>6200000</v>
@@ -75389,16 +75389,16 @@
         <v>164</v>
       </c>
       <c r="Q569" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R569" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="S569" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T569" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U569" s="3" t="s">
         <v>46</v>
@@ -75419,13 +75419,13 @@
         <v>46</v>
       </c>
       <c r="AA569" s="7">
-        <v>1856768</v>
+        <v>2102768</v>
       </c>
       <c r="AB569" s="7">
         <v>31</v>
       </c>
       <c r="AC569" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD569" s="3" t="s">
         <v>1229</v>
@@ -75434,10 +75434,10 @@
         <v>1230</v>
       </c>
       <c r="AF569" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG569" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH569" s="7">
         <v>18600000</v>
@@ -75523,7 +75523,7 @@
         <v>33</v>
       </c>
       <c r="T570" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U570" s="3" t="s">
         <v>46</v>
@@ -75550,7 +75550,7 @@
         <v>31</v>
       </c>
       <c r="AC570" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD570" s="3" t="s">
         <v>1229</v>
@@ -75559,10 +75559,10 @@
         <v>1230</v>
       </c>
       <c r="AF570" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG570" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH570" s="7">
         <v>12400000</v>
@@ -75648,7 +75648,7 @@
         <v>27</v>
       </c>
       <c r="T571" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U571" s="3" t="s">
         <v>46</v>
@@ -75675,7 +75675,7 @@
         <v>31</v>
       </c>
       <c r="AC571" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD571" s="3" t="s">
         <v>1229</v>
@@ -75684,10 +75684,10 @@
         <v>1230</v>
       </c>
       <c r="AF571" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG571" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH571" s="7">
         <v>12400000</v>
@@ -75764,16 +75764,16 @@
         <v>65</v>
       </c>
       <c r="Q572" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R572" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S572" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T572" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U572" s="3" t="s">
         <v>46</v>
@@ -75800,7 +75800,7 @@
         <v>31</v>
       </c>
       <c r="AC572" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD572" s="3" t="s">
         <v>1229</v>
@@ -75809,10 +75809,10 @@
         <v>1230</v>
       </c>
       <c r="AF572" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG572" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH572" s="7">
         <v>12400000</v>
@@ -75889,16 +75889,16 @@
         <v>79</v>
       </c>
       <c r="Q573" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R573" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S573" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T573" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U573" s="3" t="s">
         <v>46</v>
@@ -75925,7 +75925,7 @@
         <v>31</v>
       </c>
       <c r="AC573" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD573" s="3" t="s">
         <v>1229</v>
@@ -75934,10 +75934,10 @@
         <v>1230</v>
       </c>
       <c r="AF573" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG573" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH573" s="7">
         <v>12400000</v>
@@ -76023,7 +76023,7 @@
         <v>9</v>
       </c>
       <c r="T574" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U574" s="3" t="s">
         <v>46</v>
@@ -76050,7 +76050,7 @@
         <v>31</v>
       </c>
       <c r="AC574" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD574" s="3" t="s">
         <v>1229</v>
@@ -76059,10 +76059,10 @@
         <v>1230</v>
       </c>
       <c r="AF574" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG574" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH574" s="7">
         <v>12400000</v>
@@ -76139,16 +76139,16 @@
         <v>65</v>
       </c>
       <c r="Q575" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R575" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S575" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T575" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U575" s="3" t="s">
         <v>46</v>
@@ -76175,7 +76175,7 @@
         <v>31</v>
       </c>
       <c r="AC575" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD575" s="3" t="s">
         <v>1229</v>
@@ -76184,10 +76184,10 @@
         <v>1230</v>
       </c>
       <c r="AF575" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG575" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH575" s="7">
         <v>12400000</v>
@@ -76273,7 +76273,7 @@
         <v>5</v>
       </c>
       <c r="T576" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U576" s="3" t="s">
         <v>46</v>
@@ -76300,7 +76300,7 @@
         <v>31</v>
       </c>
       <c r="AC576" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD576" s="3" t="s">
         <v>1229</v>
@@ -76309,10 +76309,10 @@
         <v>1230</v>
       </c>
       <c r="AF576" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG576" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH576" s="7">
         <v>12400000</v>
@@ -76389,16 +76389,16 @@
         <v>196</v>
       </c>
       <c r="Q577" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R577" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S577" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T577" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U577" s="3" t="s">
         <v>46</v>
@@ -76425,7 +76425,7 @@
         <v>31</v>
       </c>
       <c r="AC577" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD577" s="3" t="s">
         <v>1229</v>
@@ -76434,10 +76434,10 @@
         <v>1230</v>
       </c>
       <c r="AF577" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG577" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH577" s="7">
         <v>12400000</v>
@@ -76523,7 +76523,7 @@
         <v>6</v>
       </c>
       <c r="T578" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U578" s="3" t="s">
         <v>46</v>
@@ -76550,7 +76550,7 @@
         <v>31</v>
       </c>
       <c r="AC578" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD578" s="3" t="s">
         <v>1229</v>
@@ -76559,10 +76559,10 @@
         <v>1230</v>
       </c>
       <c r="AF578" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG578" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH578" s="7">
         <v>12400000</v>
@@ -76648,7 +76648,7 @@
         <v>11</v>
       </c>
       <c r="T579" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U579" s="3" t="s">
         <v>46</v>
@@ -76675,7 +76675,7 @@
         <v>31</v>
       </c>
       <c r="AC579" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD579" s="3" t="s">
         <v>1229</v>
@@ -76684,10 +76684,10 @@
         <v>1230</v>
       </c>
       <c r="AF579" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG579" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH579" s="7">
         <v>12400000</v>
@@ -76764,16 +76764,16 @@
         <v>196</v>
       </c>
       <c r="Q580" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R580" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S580" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T580" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U580" s="3" t="s">
         <v>46</v>
@@ -76800,7 +76800,7 @@
         <v>31</v>
       </c>
       <c r="AC580" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD580" s="3" t="s">
         <v>1229</v>
@@ -76809,10 +76809,10 @@
         <v>1230</v>
       </c>
       <c r="AF580" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG580" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH580" s="7">
         <v>12400000</v>
@@ -76889,16 +76889,16 @@
         <v>157</v>
       </c>
       <c r="Q581" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R581" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S581" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T581" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U581" s="3" t="s">
         <v>46</v>
@@ -76925,7 +76925,7 @@
         <v>31</v>
       </c>
       <c r="AC581" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD581" s="3" t="s">
         <v>1229</v>
@@ -76934,10 +76934,10 @@
         <v>1230</v>
       </c>
       <c r="AF581" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG581" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH581" s="7">
         <v>12400000</v>
@@ -77023,7 +77023,7 @@
         <v>12</v>
       </c>
       <c r="T582" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U582" s="3" t="s">
         <v>46</v>
@@ -77050,7 +77050,7 @@
         <v>31</v>
       </c>
       <c r="AC582" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD582" s="3" t="s">
         <v>1229</v>
@@ -77059,10 +77059,10 @@
         <v>1230</v>
       </c>
       <c r="AF582" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG582" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH582" s="7">
         <v>12400000</v>
@@ -77148,7 +77148,7 @@
         <v>26</v>
       </c>
       <c r="T583" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U583" s="3" t="s">
         <v>46</v>
@@ -77175,7 +77175,7 @@
         <v>31</v>
       </c>
       <c r="AC583" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD583" s="3" t="s">
         <v>1229</v>
@@ -77184,10 +77184,10 @@
         <v>1230</v>
       </c>
       <c r="AF583" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG583" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH583" s="7">
         <v>12400000</v>
@@ -77264,16 +77264,16 @@
         <v>65</v>
       </c>
       <c r="Q584" s="5">
+        <v>18</v>
+      </c>
+      <c r="R584" s="5">
         <v>17</v>
       </c>
-      <c r="R584" s="5">
-        <v>16</v>
-      </c>
       <c r="S584" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T584" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U584" s="3" t="s">
         <v>46</v>
@@ -77300,7 +77300,7 @@
         <v>31</v>
       </c>
       <c r="AC584" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD584" s="3" t="s">
         <v>1229</v>
@@ -77309,10 +77309,10 @@
         <v>1230</v>
       </c>
       <c r="AF584" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG584" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH584" s="7">
         <v>12400000</v>
@@ -77389,16 +77389,16 @@
         <v>164</v>
       </c>
       <c r="Q585" s="5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R585" s="5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S585" s="5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T585" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U585" s="3" t="s">
         <v>46</v>
@@ -77425,7 +77425,7 @@
         <v>31</v>
       </c>
       <c r="AC585" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD585" s="3" t="s">
         <v>1229</v>
@@ -77434,10 +77434,10 @@
         <v>1230</v>
       </c>
       <c r="AF585" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG585" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH585" s="7">
         <v>12400000</v>
@@ -77523,7 +77523,7 @@
         <v>13</v>
       </c>
       <c r="T586" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U586" s="3" t="s">
         <v>46</v>
@@ -77544,13 +77544,13 @@
         <v>46</v>
       </c>
       <c r="AA586" s="7">
-        <v>2332210</v>
+        <v>4678207</v>
       </c>
       <c r="AB586" s="7">
         <v>31</v>
       </c>
       <c r="AC586" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD586" s="3" t="s">
         <v>1229</v>
@@ -77559,10 +77559,10 @@
         <v>1230</v>
       </c>
       <c r="AF586" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG586" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH586" s="7">
         <v>12400000</v>
@@ -77639,16 +77639,16 @@
         <v>157</v>
       </c>
       <c r="Q587" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R587" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S587" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T587" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U587" s="3" t="s">
         <v>46</v>
@@ -77675,7 +77675,7 @@
         <v>31</v>
       </c>
       <c r="AC587" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD587" s="3" t="s">
         <v>1229</v>
@@ -77684,10 +77684,10 @@
         <v>1230</v>
       </c>
       <c r="AF587" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG587" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH587" s="7">
         <v>12400000</v>
@@ -77773,7 +77773,7 @@
         <v>33</v>
       </c>
       <c r="T588" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U588" s="3" t="s">
         <v>46</v>
@@ -77800,7 +77800,7 @@
         <v>31</v>
       </c>
       <c r="AC588" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD588" s="3" t="s">
         <v>1229</v>
@@ -77809,10 +77809,10 @@
         <v>1230</v>
       </c>
       <c r="AF588" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG588" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH588" s="7">
         <v>6200000</v>
@@ -77898,7 +77898,7 @@
         <v>27</v>
       </c>
       <c r="T589" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U589" s="3" t="s">
         <v>46</v>
@@ -77925,7 +77925,7 @@
         <v>31</v>
       </c>
       <c r="AC589" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD589" s="3" t="s">
         <v>1229</v>
@@ -77934,10 +77934,10 @@
         <v>1230</v>
       </c>
       <c r="AF589" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG589" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH589" s="7">
         <v>6200000</v>
@@ -78023,7 +78023,7 @@
         <v>8</v>
       </c>
       <c r="T590" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U590" s="3" t="s">
         <v>46</v>
@@ -78050,7 +78050,7 @@
         <v>31</v>
       </c>
       <c r="AC590" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD590" s="3" t="s">
         <v>1229</v>
@@ -78059,10 +78059,10 @@
         <v>1230</v>
       </c>
       <c r="AF590" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG590" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH590" s="7">
         <v>6200000</v>
@@ -78139,16 +78139,16 @@
         <v>79</v>
       </c>
       <c r="Q591" s="5">
+        <v>30</v>
+      </c>
+      <c r="R591" s="5">
         <v>29</v>
       </c>
-      <c r="R591" s="5">
-        <v>28</v>
-      </c>
       <c r="S591" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T591" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U591" s="3" t="s">
         <v>46</v>
@@ -78175,7 +78175,7 @@
         <v>31</v>
       </c>
       <c r="AC591" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD591" s="3" t="s">
         <v>1229</v>
@@ -78184,10 +78184,10 @@
         <v>1230</v>
       </c>
       <c r="AF591" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG591" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH591" s="7">
         <v>6200000</v>
@@ -78273,7 +78273,7 @@
         <v>9</v>
       </c>
       <c r="T592" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U592" s="3" t="s">
         <v>46</v>
@@ -78300,7 +78300,7 @@
         <v>31</v>
       </c>
       <c r="AC592" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD592" s="3" t="s">
         <v>1229</v>
@@ -78309,10 +78309,10 @@
         <v>1230</v>
       </c>
       <c r="AF592" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG592" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH592" s="7">
         <v>6200000</v>
@@ -78389,16 +78389,16 @@
         <v>79</v>
       </c>
       <c r="Q593" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R593" s="3">
         <v>0</v>
       </c>
       <c r="S593" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T593" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U593" s="3" t="s">
         <v>46</v>
@@ -78425,7 +78425,7 @@
         <v>31</v>
       </c>
       <c r="AC593" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD593" s="3" t="s">
         <v>1229</v>
@@ -78434,10 +78434,10 @@
         <v>1230</v>
       </c>
       <c r="AF593" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG593" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH593" s="7">
         <v>6200000</v>
@@ -78523,7 +78523,7 @@
         <v>16</v>
       </c>
       <c r="T594" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U594" s="3" t="s">
         <v>46</v>
@@ -78550,7 +78550,7 @@
         <v>31</v>
       </c>
       <c r="AC594" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD594" s="3" t="s">
         <v>1229</v>
@@ -78559,10 +78559,10 @@
         <v>1230</v>
       </c>
       <c r="AF594" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG594" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH594" s="7">
         <v>6200000</v>
@@ -78648,7 +78648,7 @@
         <v>6</v>
       </c>
       <c r="T595" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U595" s="3" t="s">
         <v>46</v>
@@ -78675,7 +78675,7 @@
         <v>31</v>
       </c>
       <c r="AC595" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD595" s="3" t="s">
         <v>1229</v>
@@ -78684,10 +78684,10 @@
         <v>1230</v>
       </c>
       <c r="AF595" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG595" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH595" s="7">
         <v>6200000</v>
@@ -78764,16 +78764,16 @@
         <v>196</v>
       </c>
       <c r="Q596" s="5">
+        <v>17</v>
+      </c>
+      <c r="R596" s="5">
         <v>16</v>
       </c>
-      <c r="R596" s="5">
-        <v>15</v>
-      </c>
       <c r="S596" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T596" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U596" s="3" t="s">
         <v>46</v>
@@ -78800,7 +78800,7 @@
         <v>31</v>
       </c>
       <c r="AC596" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD596" s="3" t="s">
         <v>1229</v>
@@ -78809,10 +78809,10 @@
         <v>1230</v>
       </c>
       <c r="AF596" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG596" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH596" s="7">
         <v>6200000</v>
@@ -78889,16 +78889,16 @@
         <v>196</v>
       </c>
       <c r="Q597" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R597" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S597" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T597" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U597" s="3" t="s">
         <v>46</v>
@@ -78925,7 +78925,7 @@
         <v>31</v>
       </c>
       <c r="AC597" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD597" s="3" t="s">
         <v>1229</v>
@@ -78934,10 +78934,10 @@
         <v>1230</v>
       </c>
       <c r="AF597" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG597" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH597" s="7">
         <v>6200000</v>
@@ -79023,7 +79023,7 @@
         <v>17</v>
       </c>
       <c r="T598" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U598" s="3" t="s">
         <v>46</v>
@@ -79050,7 +79050,7 @@
         <v>31</v>
       </c>
       <c r="AC598" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD598" s="3" t="s">
         <v>1229</v>
@@ -79059,10 +79059,10 @@
         <v>1230</v>
       </c>
       <c r="AF598" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG598" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH598" s="7">
         <v>6200000</v>
@@ -79139,16 +79139,16 @@
         <v>65</v>
       </c>
       <c r="Q599" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R599" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S599" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T599" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U599" s="3" t="s">
         <v>46</v>
@@ -79175,7 +79175,7 @@
         <v>31</v>
       </c>
       <c r="AC599" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD599" s="3" t="s">
         <v>1229</v>
@@ -79184,10 +79184,10 @@
         <v>1230</v>
       </c>
       <c r="AF599" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG599" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH599" s="7">
         <v>6200000</v>
@@ -79273,7 +79273,7 @@
         <v>8</v>
       </c>
       <c r="T600" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U600" s="3" t="s">
         <v>46</v>
@@ -79294,13 +79294,13 @@
         <v>46</v>
       </c>
       <c r="AA600" s="7">
-        <v>690000</v>
+        <v>1145000</v>
       </c>
       <c r="AB600" s="7">
         <v>31</v>
       </c>
       <c r="AC600" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD600" s="3" t="s">
         <v>1229</v>
@@ -79309,10 +79309,10 @@
         <v>1230</v>
       </c>
       <c r="AF600" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG600" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH600" s="7">
         <v>6200000</v>
@@ -79398,7 +79398,7 @@
         <v>7</v>
       </c>
       <c r="T601" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U601" s="3" t="s">
         <v>46</v>
@@ -79425,7 +79425,7 @@
         <v>31</v>
       </c>
       <c r="AC601" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD601" s="3" t="s">
         <v>1229</v>
@@ -79434,10 +79434,10 @@
         <v>1230</v>
       </c>
       <c r="AF601" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG601" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH601" s="7">
         <v>6200000</v>
@@ -79514,16 +79514,16 @@
         <v>150</v>
       </c>
       <c r="Q602" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R602" s="5">
         <v>5</v>
       </c>
       <c r="S602" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T602" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U602" s="3" t="s">
         <v>46</v>
@@ -79550,7 +79550,7 @@
         <v>31</v>
       </c>
       <c r="AC602" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD602" s="3" t="s">
         <v>1229</v>
@@ -79559,10 +79559,10 @@
         <v>1230</v>
       </c>
       <c r="AF602" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG602" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH602" s="7">
         <v>6200000</v>
@@ -79648,7 +79648,7 @@
         <v>8</v>
       </c>
       <c r="T603" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U603" s="3" t="s">
         <v>46</v>
@@ -79669,13 +79669,13 @@
         <v>46</v>
       </c>
       <c r="AA603" s="7">
-        <v>694460</v>
+        <v>1377560</v>
       </c>
       <c r="AB603" s="7">
         <v>31</v>
       </c>
       <c r="AC603" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD603" s="3" t="s">
         <v>1229</v>
@@ -79684,10 +79684,10 @@
         <v>1230</v>
       </c>
       <c r="AF603" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG603" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH603" s="7">
         <v>6200000</v>
@@ -79773,7 +79773,7 @@
         <v>5</v>
       </c>
       <c r="T604" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U604" s="3" t="s">
         <v>46</v>
@@ -79794,13 +79794,13 @@
         <v>46</v>
       </c>
       <c r="AA604" s="7">
-        <v>935250</v>
+        <v>1330250</v>
       </c>
       <c r="AB604" s="7">
         <v>31</v>
       </c>
       <c r="AC604" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD604" s="3" t="s">
         <v>1229</v>
@@ -79809,10 +79809,10 @@
         <v>1230</v>
       </c>
       <c r="AF604" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG604" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH604" s="7">
         <v>6200000</v>
@@ -79889,16 +79889,16 @@
         <v>130</v>
       </c>
       <c r="Q605" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R605" s="5">
         <v>7</v>
       </c>
       <c r="S605" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T605" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U605" s="3" t="s">
         <v>46</v>
@@ -79925,7 +79925,7 @@
         <v>31</v>
       </c>
       <c r="AC605" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD605" s="3" t="s">
         <v>1229</v>
@@ -79934,10 +79934,10 @@
         <v>1230</v>
       </c>
       <c r="AF605" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG605" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH605" s="7">
         <v>6200000</v>
@@ -80023,7 +80023,7 @@
         <v>2</v>
       </c>
       <c r="T606" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U606" s="3" t="s">
         <v>46</v>
@@ -80043,14 +80043,14 @@
       <c r="Z606" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA606" s="3" t="s">
-        <v>46</v>
+      <c r="AA606" s="7">
+        <v>156000</v>
       </c>
       <c r="AB606" s="7">
         <v>31</v>
       </c>
       <c r="AC606" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD606" s="3" t="s">
         <v>1229</v>
@@ -80059,10 +80059,10 @@
         <v>1230</v>
       </c>
       <c r="AF606" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG606" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH606" s="7">
         <v>6200000</v>
@@ -80139,16 +80139,16 @@
         <v>196</v>
       </c>
       <c r="Q607" s="5">
+        <v>29</v>
+      </c>
+      <c r="R607" s="5">
         <v>28</v>
       </c>
-      <c r="R607" s="5">
-        <v>27</v>
-      </c>
       <c r="S607" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T607" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U607" s="3" t="s">
         <v>46</v>
@@ -80175,7 +80175,7 @@
         <v>31</v>
       </c>
       <c r="AC607" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD607" s="3" t="s">
         <v>1229</v>
@@ -80184,10 +80184,10 @@
         <v>1230</v>
       </c>
       <c r="AF607" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG607" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH607" s="7">
         <v>6200000</v>
@@ -80264,16 +80264,16 @@
         <v>157</v>
       </c>
       <c r="Q608" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R608" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S608" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T608" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U608" s="3" t="s">
         <v>46</v>
@@ -80300,7 +80300,7 @@
         <v>31</v>
       </c>
       <c r="AC608" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD608" s="3" t="s">
         <v>1229</v>
@@ -80309,10 +80309,10 @@
         <v>1230</v>
       </c>
       <c r="AF608" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG608" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH608" s="7">
         <v>6200000</v>
@@ -80389,16 +80389,16 @@
         <v>157</v>
       </c>
       <c r="Q609" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R609" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S609" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T609" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U609" s="3" t="s">
         <v>46</v>
@@ -80425,7 +80425,7 @@
         <v>31</v>
       </c>
       <c r="AC609" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD609" s="3" t="s">
         <v>1229</v>
@@ -80434,10 +80434,10 @@
         <v>1230</v>
       </c>
       <c r="AF609" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG609" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH609" s="7">
         <v>6200000</v>
@@ -80523,7 +80523,7 @@
         <v>3</v>
       </c>
       <c r="T610" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U610" s="3" t="s">
         <v>46</v>
@@ -80550,7 +80550,7 @@
         <v>31</v>
       </c>
       <c r="AC610" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD610" s="3" t="s">
         <v>1229</v>
@@ -80559,10 +80559,10 @@
         <v>1230</v>
       </c>
       <c r="AF610" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG610" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH610" s="7">
         <v>6200000</v>
@@ -80648,7 +80648,7 @@
         <v>9</v>
       </c>
       <c r="T611" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U611" s="3" t="s">
         <v>46</v>
@@ -80675,7 +80675,7 @@
         <v>31</v>
       </c>
       <c r="AC611" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD611" s="3" t="s">
         <v>1229</v>
@@ -80684,10 +80684,10 @@
         <v>1230</v>
       </c>
       <c r="AF611" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG611" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH611" s="7">
         <v>6200000</v>
@@ -80773,7 +80773,7 @@
         <v>6</v>
       </c>
       <c r="T612" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U612" s="3" t="s">
         <v>46</v>
@@ -80794,13 +80794,13 @@
         <v>46</v>
       </c>
       <c r="AA612" s="7">
-        <v>1033851</v>
+        <v>1419851</v>
       </c>
       <c r="AB612" s="7">
         <v>31</v>
       </c>
       <c r="AC612" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD612" s="3" t="s">
         <v>1229</v>
@@ -80809,10 +80809,10 @@
         <v>1230</v>
       </c>
       <c r="AF612" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG612" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH612" s="7">
         <v>6200000</v>
@@ -80898,7 +80898,7 @@
         <v>7</v>
       </c>
       <c r="T613" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U613" s="3" t="s">
         <v>46</v>
@@ -80919,13 +80919,13 @@
         <v>46</v>
       </c>
       <c r="AA613" s="7">
-        <v>243297</v>
+        <v>703297</v>
       </c>
       <c r="AB613" s="7">
         <v>31</v>
       </c>
       <c r="AC613" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD613" s="3" t="s">
         <v>1229</v>
@@ -80934,10 +80934,10 @@
         <v>1230</v>
       </c>
       <c r="AF613" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG613" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH613" s="7">
         <v>6200000</v>
@@ -81023,7 +81023,7 @@
         <v>1</v>
       </c>
       <c r="T614" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U614" s="3" t="s">
         <v>46</v>
@@ -81050,7 +81050,7 @@
         <v>31</v>
       </c>
       <c r="AC614" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD614" s="3" t="s">
         <v>1229</v>
@@ -81059,10 +81059,10 @@
         <v>1230</v>
       </c>
       <c r="AF614" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG614" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH614" s="7">
         <v>6200000</v>
@@ -81139,16 +81139,16 @@
         <v>196</v>
       </c>
       <c r="Q615" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R615" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S615" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T615" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U615" s="3" t="s">
         <v>46</v>
@@ -81175,7 +81175,7 @@
         <v>31</v>
       </c>
       <c r="AC615" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD615" s="3" t="s">
         <v>1229</v>
@@ -81184,10 +81184,10 @@
         <v>1230</v>
       </c>
       <c r="AF615" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG615" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH615" s="7">
         <v>6200000</v>
@@ -81273,7 +81273,7 @@
         <v>8</v>
       </c>
       <c r="T616" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U616" s="3" t="s">
         <v>46</v>
@@ -81300,7 +81300,7 @@
         <v>31</v>
       </c>
       <c r="AC616" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD616" s="3" t="s">
         <v>1229</v>
@@ -81309,10 +81309,10 @@
         <v>1230</v>
       </c>
       <c r="AF616" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG616" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH616" s="7">
         <v>6200000</v>
@@ -81398,7 +81398,7 @@
         <v>14</v>
       </c>
       <c r="T617" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U617" s="3" t="s">
         <v>46</v>
@@ -81425,7 +81425,7 @@
         <v>31</v>
       </c>
       <c r="AC617" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD617" s="3" t="s">
         <v>1229</v>
@@ -81434,10 +81434,10 @@
         <v>1230</v>
       </c>
       <c r="AF617" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG617" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH617" s="7">
         <v>6200000</v>
@@ -81523,7 +81523,7 @@
         <v>8</v>
       </c>
       <c r="T618" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U618" s="3" t="s">
         <v>46</v>
@@ -81544,13 +81544,13 @@
         <v>46</v>
       </c>
       <c r="AA618" s="7">
-        <v>468000</v>
+        <v>2401350</v>
       </c>
       <c r="AB618" s="7">
         <v>31</v>
       </c>
       <c r="AC618" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD618" s="3" t="s">
         <v>1229</v>
@@ -81559,10 +81559,10 @@
         <v>1230</v>
       </c>
       <c r="AF618" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG618" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH618" s="7">
         <v>6200000</v>
@@ -81639,16 +81639,16 @@
         <v>196</v>
       </c>
       <c r="Q619" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R619" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S619" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T619" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U619" s="3" t="s">
         <v>46</v>
@@ -81675,7 +81675,7 @@
         <v>31</v>
       </c>
       <c r="AC619" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD619" s="3" t="s">
         <v>1229</v>
@@ -81684,10 +81684,10 @@
         <v>1230</v>
       </c>
       <c r="AF619" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG619" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH619" s="7">
         <v>6200000</v>
@@ -81767,13 +81767,13 @@
         <v>10</v>
       </c>
       <c r="R620" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S620" s="5">
         <v>10</v>
       </c>
       <c r="T620" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U620" s="3" t="s">
         <v>46</v>
@@ -81800,7 +81800,7 @@
         <v>31</v>
       </c>
       <c r="AC620" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD620" s="3" t="s">
         <v>1229</v>
@@ -81809,10 +81809,10 @@
         <v>1230</v>
       </c>
       <c r="AF620" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG620" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH620" s="7">
         <v>6200000</v>
@@ -81898,7 +81898,7 @@
         <v>6</v>
       </c>
       <c r="T621" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U621" s="3" t="s">
         <v>46</v>
@@ -81925,7 +81925,7 @@
         <v>31</v>
       </c>
       <c r="AC621" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD621" s="3" t="s">
         <v>1229</v>
@@ -81934,10 +81934,10 @@
         <v>1230</v>
       </c>
       <c r="AF621" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG621" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH621" s="7">
         <v>6200000</v>
@@ -82023,7 +82023,7 @@
         <v>25</v>
       </c>
       <c r="T622" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U622" s="3" t="s">
         <v>46</v>
@@ -82050,7 +82050,7 @@
         <v>31</v>
       </c>
       <c r="AC622" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD622" s="3" t="s">
         <v>1229</v>
@@ -82059,10 +82059,10 @@
         <v>1230</v>
       </c>
       <c r="AF622" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG622" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH622" s="7">
         <v>6200000</v>
@@ -82139,16 +82139,16 @@
         <v>203</v>
       </c>
       <c r="Q623" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R623" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S623" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T623" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U623" s="3" t="s">
         <v>46</v>
@@ -82169,13 +82169,13 @@
         <v>46</v>
       </c>
       <c r="AA623" s="7">
-        <v>286618</v>
+        <v>984568</v>
       </c>
       <c r="AB623" s="7">
         <v>31</v>
       </c>
       <c r="AC623" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD623" s="3" t="s">
         <v>1229</v>
@@ -82184,10 +82184,10 @@
         <v>1230</v>
       </c>
       <c r="AF623" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG623" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH623" s="7">
         <v>6200000</v>
@@ -82264,16 +82264,16 @@
         <v>65</v>
       </c>
       <c r="Q624" s="5">
+        <v>29</v>
+      </c>
+      <c r="R624" s="5">
         <v>28</v>
       </c>
-      <c r="R624" s="5">
-        <v>27</v>
-      </c>
       <c r="S624" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T624" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U624" s="3" t="s">
         <v>46</v>
@@ -82300,7 +82300,7 @@
         <v>31</v>
       </c>
       <c r="AC624" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD624" s="3" t="s">
         <v>1229</v>
@@ -82309,10 +82309,10 @@
         <v>1230</v>
       </c>
       <c r="AF624" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG624" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH624" s="7">
         <v>6200000</v>
@@ -82398,7 +82398,7 @@
         <v>5</v>
       </c>
       <c r="T625" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U625" s="3" t="s">
         <v>46</v>
@@ -82425,7 +82425,7 @@
         <v>31</v>
       </c>
       <c r="AC625" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD625" s="3" t="s">
         <v>1229</v>
@@ -82434,10 +82434,10 @@
         <v>1230</v>
       </c>
       <c r="AF625" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG625" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH625" s="7">
         <v>6200000</v>
@@ -82514,16 +82514,16 @@
         <v>79</v>
       </c>
       <c r="Q626" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R626" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S626" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T626" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U626" s="3" t="s">
         <v>46</v>
@@ -82550,7 +82550,7 @@
         <v>31</v>
       </c>
       <c r="AC626" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD626" s="3" t="s">
         <v>1229</v>
@@ -82559,10 +82559,10 @@
         <v>1230</v>
       </c>
       <c r="AF626" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG626" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH626" s="7">
         <v>6200000</v>
@@ -82639,16 +82639,16 @@
         <v>79</v>
       </c>
       <c r="Q627" s="5">
+        <v>28</v>
+      </c>
+      <c r="R627" s="5">
         <v>27</v>
       </c>
-      <c r="R627" s="5">
-        <v>26</v>
-      </c>
       <c r="S627" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T627" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U627" s="3" t="s">
         <v>46</v>
@@ -82675,7 +82675,7 @@
         <v>31</v>
       </c>
       <c r="AC627" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD627" s="3" t="s">
         <v>1229</v>
@@ -82684,10 +82684,10 @@
         <v>1230</v>
       </c>
       <c r="AF627" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG627" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH627" s="7">
         <v>6200000</v>
@@ -82773,7 +82773,7 @@
         <v>9</v>
       </c>
       <c r="T628" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U628" s="3" t="s">
         <v>46</v>
@@ -82800,7 +82800,7 @@
         <v>31</v>
       </c>
       <c r="AC628" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD628" s="3" t="s">
         <v>1229</v>
@@ -82809,10 +82809,10 @@
         <v>1230</v>
       </c>
       <c r="AF628" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG628" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH628" s="7">
         <v>6200000</v>
@@ -82898,7 +82898,7 @@
         <v>2</v>
       </c>
       <c r="T629" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="U629" s="3" t="s">
         <v>46</v>
@@ -82925,7 +82925,7 @@
         <v>31</v>
       </c>
       <c r="AC629" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="AD629" s="3" t="s">
         <v>1229</v>
@@ -82934,10 +82934,10 @@
         <v>1230</v>
       </c>
       <c r="AF629" s="3" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="AG629" s="3" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="AH629" s="7">
         <v>6200000</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -65139,13 +65139,13 @@
         <v>196</v>
       </c>
       <c r="Q487" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R487" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S487" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T487" s="3" t="s">
         <v>1207</v>
@@ -66889,13 +66889,13 @@
         <v>196</v>
       </c>
       <c r="Q501" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R501" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S501" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T501" s="3" t="s">
         <v>1207</v>
@@ -68514,13 +68514,13 @@
         <v>196</v>
       </c>
       <c r="Q514" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R514" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S514" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T514" s="3" t="s">
         <v>1207</v>
@@ -72264,13 +72264,13 @@
         <v>210</v>
       </c>
       <c r="Q544" s="5">
+        <v>4</v>
+      </c>
+      <c r="R544" s="5">
         <v>3</v>
       </c>
-      <c r="R544" s="5">
-        <v>2</v>
-      </c>
       <c r="S544" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T544" s="3" t="s">
         <v>1207</v>
@@ -74139,13 +74139,13 @@
         <v>196</v>
       </c>
       <c r="Q559" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R559" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S559" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T559" s="3" t="s">
         <v>1207</v>
@@ -76389,13 +76389,13 @@
         <v>196</v>
       </c>
       <c r="Q577" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R577" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S577" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T577" s="3" t="s">
         <v>1207</v>
@@ -80139,13 +80139,13 @@
         <v>196</v>
       </c>
       <c r="Q607" s="5">
+        <v>30</v>
+      </c>
+      <c r="R607" s="5">
         <v>29</v>
       </c>
-      <c r="R607" s="5">
-        <v>28</v>
-      </c>
       <c r="S607" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T607" s="3" t="s">
         <v>1207</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18937" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18931" uniqueCount="1341">
   <si>
     <t>DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH</t>
   </si>
@@ -3388,6 +3388,21 @@
     <t>1039, Phạm Văn Đồng</t>
   </si>
   <si>
+    <t>3057973</t>
+  </si>
+  <si>
+    <t>Hùng Anh</t>
+  </si>
+  <si>
+    <t>23, Đường 100</t>
+  </si>
+  <si>
+    <t>3142121</t>
+  </si>
+  <si>
+    <t>Anh Đại</t>
+  </si>
+  <si>
     <t>2800</t>
   </si>
   <si>
@@ -3397,21 +3412,6 @@
     <t>18/27, Đại Học</t>
   </si>
   <si>
-    <t>3057973</t>
-  </si>
-  <si>
-    <t>Hùng Anh</t>
-  </si>
-  <si>
-    <t>23, Đường 100</t>
-  </si>
-  <si>
-    <t>3142121</t>
-  </si>
-  <si>
-    <t>Anh Đại</t>
-  </si>
-  <si>
     <t>5355</t>
   </si>
   <si>
@@ -3457,6 +3457,15 @@
     <t>Lầu 2 toà A1, Đại Học Quốc Tế</t>
   </si>
   <si>
+    <t>3057968</t>
+  </si>
+  <si>
+    <t>Anh Hùng ( Trái Cây )</t>
+  </si>
+  <si>
+    <t>71, Đình Phong Phú</t>
+  </si>
+  <si>
     <t>5028</t>
   </si>
   <si>
@@ -3466,15 +3475,6 @@
     <t xml:space="preserve">108, Đường 4 Đại Học Nông Lâm </t>
   </si>
   <si>
-    <t>3057968</t>
-  </si>
-  <si>
-    <t>Anh Hùng ( Trái Cây )</t>
-  </si>
-  <si>
-    <t>71, Đình Phong Phú</t>
-  </si>
-  <si>
     <t>2340641</t>
   </si>
   <si>
@@ -3514,6 +3514,15 @@
     <t>203, Man Thiện</t>
   </si>
   <si>
+    <t>3265</t>
+  </si>
+  <si>
+    <t>Thu Hiền</t>
+  </si>
+  <si>
+    <t>235, Tăng Nhơn Phú</t>
+  </si>
+  <si>
     <t>3638</t>
   </si>
   <si>
@@ -3529,15 +3538,6 @@
     <t>5, Ngô Quyền</t>
   </si>
   <si>
-    <t>3265</t>
-  </si>
-  <si>
-    <t>Thu Hiền</t>
-  </si>
-  <si>
-    <t>235, Tăng Nhơn Phú</t>
-  </si>
-  <si>
     <t>Mức 2 - Kệ Mô Hình</t>
   </si>
   <si>
@@ -3568,19 +3568,19 @@
     <t>MSC_Cuộc thi ảnh Đại sứ Ngành hàng Gia Vị_HCM_All2026_T10</t>
   </si>
   <si>
+    <t>2430771</t>
+  </si>
+  <si>
+    <t>Tạp Hóa Vinh Phát</t>
+  </si>
+  <si>
+    <t>208/6B, Đường 138</t>
+  </si>
+  <si>
     <t>2790031</t>
   </si>
   <si>
     <t>Cao Ốc Xanh</t>
-  </si>
-  <si>
-    <t>2430771</t>
-  </si>
-  <si>
-    <t>Tạp Hóa Vinh Phát</t>
-  </si>
-  <si>
-    <t>208/6B, Đường 138</t>
   </si>
   <si>
     <t>4107</t>
@@ -57861,28 +57861,28 @@
         <v>46</v>
       </c>
       <c r="I430" s="3" t="s">
-        <v>269</v>
+        <v>1125</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>270</v>
+        <v>1126</v>
       </c>
       <c r="K430" s="3" t="s">
-        <v>271</v>
+        <v>1127</v>
       </c>
       <c r="L430" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M430" s="3" t="s">
-        <v>137</v>
+        <v>51</v>
       </c>
       <c r="N430" s="3" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="O430" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="P430" s="3" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="Q430" s="3" t="s">
         <v>46</v>
@@ -57945,7 +57945,7 @@
         <v>58</v>
       </c>
       <c r="AK430" s="6">
-        <v>46301.91933796296</v>
+        <v>46324.30341940973</v>
       </c>
       <c r="AL430" s="3" t="s">
         <v>46</v>
@@ -57957,7 +57957,7 @@
         <v>58</v>
       </c>
       <c r="AO430" s="6">
-        <v>46301.91933796296</v>
+        <v>46324.30341940973</v>
       </c>
     </row>
     <row r="431" spans="1:41" x14ac:dyDescent="0.25">
@@ -57986,28 +57986,28 @@
         <v>46</v>
       </c>
       <c r="I431" s="3" t="s">
-        <v>340</v>
+        <v>1128</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>341</v>
+        <v>1129</v>
       </c>
       <c r="K431" s="3" t="s">
-        <v>342</v>
+        <v>104</v>
       </c>
       <c r="L431" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M431" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="N431" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O431" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="P431" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="Q431" s="3" t="s">
         <v>46</v>
@@ -58070,7 +58070,7 @@
         <v>58</v>
       </c>
       <c r="AK431" s="6">
-        <v>46307.90555991898</v>
+        <v>46301.91933796296</v>
       </c>
       <c r="AL431" s="3" t="s">
         <v>46</v>
@@ -58082,7 +58082,7 @@
         <v>58</v>
       </c>
       <c r="AO431" s="6">
-        <v>46307.90555991898</v>
+        <v>46301.91933796296</v>
       </c>
     </row>
     <row r="432" spans="1:41" x14ac:dyDescent="0.25">
@@ -58111,28 +58111,28 @@
         <v>46</v>
       </c>
       <c r="I432" s="3" t="s">
-        <v>1125</v>
+        <v>579</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1126</v>
+        <v>580</v>
       </c>
       <c r="K432" s="3" t="s">
-        <v>1127</v>
+        <v>581</v>
       </c>
       <c r="L432" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M432" s="3" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="N432" s="3" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="O432" s="3" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="P432" s="3" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="Q432" s="3" t="s">
         <v>46</v>
@@ -58236,28 +58236,28 @@
         <v>46</v>
       </c>
       <c r="I433" s="3" t="s">
-        <v>1128</v>
+        <v>340</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1129</v>
+        <v>341</v>
       </c>
       <c r="K433" s="3" t="s">
-        <v>1130</v>
+        <v>342</v>
       </c>
       <c r="L433" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M433" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="N433" s="3" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="O433" s="3" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="P433" s="3" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="Q433" s="3" t="s">
         <v>46</v>
@@ -58320,7 +58320,7 @@
         <v>58</v>
       </c>
       <c r="AK433" s="6">
-        <v>46324.30341940973</v>
+        <v>46307.90555991898</v>
       </c>
       <c r="AL433" s="3" t="s">
         <v>46</v>
@@ -58332,7 +58332,7 @@
         <v>58</v>
       </c>
       <c r="AO433" s="6">
-        <v>46324.30341940973</v>
+        <v>46307.90555991898</v>
       </c>
     </row>
     <row r="434" spans="1:41" x14ac:dyDescent="0.25">
@@ -58361,28 +58361,28 @@
         <v>46</v>
       </c>
       <c r="I434" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J434" s="3" t="s">
         <v>1131</v>
       </c>
-      <c r="J434" s="3" t="s">
+      <c r="K434" s="3" t="s">
         <v>1132</v>
-      </c>
-      <c r="K434" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="L434" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M434" s="3" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="N434" s="3" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O434" s="3" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="P434" s="3" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="Q434" s="3" t="s">
         <v>46</v>
@@ -58486,28 +58486,28 @@
         <v>46</v>
       </c>
       <c r="I435" s="3" t="s">
-        <v>579</v>
+        <v>1133</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>580</v>
+        <v>1134</v>
       </c>
       <c r="K435" s="3" t="s">
-        <v>581</v>
+        <v>1135</v>
       </c>
       <c r="L435" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M435" s="3" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="N435" s="3" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="O435" s="3" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="P435" s="3" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="Q435" s="3" t="s">
         <v>46</v>
@@ -58570,7 +58570,7 @@
         <v>58</v>
       </c>
       <c r="AK435" s="6">
-        <v>46301.91933796296</v>
+        <v>46324.30341940973</v>
       </c>
       <c r="AL435" s="3" t="s">
         <v>46</v>
@@ -58582,7 +58582,7 @@
         <v>58</v>
       </c>
       <c r="AO435" s="6">
-        <v>46301.91933796296</v>
+        <v>46324.30341940973</v>
       </c>
     </row>
     <row r="436" spans="1:41" x14ac:dyDescent="0.25">
@@ -58608,31 +58608,31 @@
         <v>45</v>
       </c>
       <c r="H436" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I436" s="3" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="K436" s="3" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="L436" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M436" s="3" t="s">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="N436" s="3" t="s">
-        <v>201</v>
+        <v>115</v>
       </c>
       <c r="O436" s="3" t="s">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="P436" s="3" t="s">
-        <v>203</v>
+        <v>117</v>
       </c>
       <c r="Q436" s="3" t="s">
         <v>46</v>
@@ -58644,7 +58644,7 @@
         <v>46</v>
       </c>
       <c r="T436" s="3" t="s">
-        <v>46</v>
+        <v>1139</v>
       </c>
       <c r="U436" s="3" t="s">
         <v>46</v>
@@ -58661,41 +58661,41 @@
       <c r="Y436" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z436" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA436" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB436" s="3" t="s">
-        <v>46</v>
+      <c r="Z436" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA436" s="7">
+        <v>11</v>
+      </c>
+      <c r="AB436" s="7">
+        <v>1</v>
       </c>
       <c r="AC436" s="3" t="s">
-        <v>46</v>
+        <v>1140</v>
       </c>
       <c r="AD436" s="3" t="s">
-        <v>46</v>
+        <v>1141</v>
       </c>
       <c r="AE436" s="3" t="s">
-        <v>46</v>
+        <v>1142</v>
       </c>
       <c r="AF436" s="3" t="s">
-        <v>46</v>
+        <v>1143</v>
       </c>
       <c r="AG436" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH436" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI436" s="3" t="s">
-        <v>46</v>
+        <v>1144</v>
+      </c>
+      <c r="AH436" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI436" s="3">
+        <v>0</v>
       </c>
       <c r="AJ436" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK436" s="6">
-        <v>46324.30341940973</v>
+        <v>46316.57381339121</v>
       </c>
       <c r="AL436" s="3" t="s">
         <v>46</v>
@@ -58707,7 +58707,7 @@
         <v>58</v>
       </c>
       <c r="AO436" s="6">
-        <v>46324.30341940973</v>
+        <v>46316.57381339121</v>
       </c>
     </row>
     <row r="437" spans="1:41" x14ac:dyDescent="0.25">
@@ -58736,13 +58736,13 @@
         <v>45</v>
       </c>
       <c r="I437" s="3" t="s">
-        <v>1136</v>
+        <v>1145</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>1137</v>
+        <v>1146</v>
       </c>
       <c r="K437" s="3" t="s">
-        <v>1138</v>
+        <v>1147</v>
       </c>
       <c r="L437" s="3" t="s">
         <v>50</v>
@@ -58790,7 +58790,7 @@
         <v>10</v>
       </c>
       <c r="AA437" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB437" s="7">
         <v>1</v>
@@ -58820,7 +58820,7 @@
         <v>58</v>
       </c>
       <c r="AK437" s="6">
-        <v>46316.57381339121</v>
+        <v>46303.59298695602</v>
       </c>
       <c r="AL437" s="3" t="s">
         <v>46</v>
@@ -58832,7 +58832,7 @@
         <v>58</v>
       </c>
       <c r="AO437" s="6">
-        <v>46316.57381339121</v>
+        <v>46303.59298695602</v>
       </c>
     </row>
     <row r="438" spans="1:41" x14ac:dyDescent="0.25">
@@ -58861,28 +58861,28 @@
         <v>45</v>
       </c>
       <c r="I438" s="3" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="K438" s="3" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="L438" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M438" s="3" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="N438" s="3" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="O438" s="3" t="s">
-        <v>116</v>
+        <v>195</v>
       </c>
       <c r="P438" s="3" t="s">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="Q438" s="3" t="s">
         <v>46</v>
@@ -58915,7 +58915,7 @@
         <v>10</v>
       </c>
       <c r="AA438" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AB438" s="7">
         <v>1</v>
@@ -58945,7 +58945,7 @@
         <v>58</v>
       </c>
       <c r="AK438" s="6">
-        <v>46303.59298695602</v>
+        <v>46307.90555991898</v>
       </c>
       <c r="AL438" s="3" t="s">
         <v>46</v>
@@ -58957,7 +58957,7 @@
         <v>58</v>
       </c>
       <c r="AO438" s="6">
-        <v>46303.59298695602</v>
+        <v>46307.90555991898</v>
       </c>
     </row>
     <row r="439" spans="1:41" x14ac:dyDescent="0.25">
@@ -58986,13 +58986,13 @@
         <v>45</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="K439" s="3" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="L439" s="3" t="s">
         <v>50</v>
@@ -59111,13 +59111,13 @@
         <v>45</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="K440" s="3" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="L440" s="3" t="s">
         <v>50</v>
@@ -59165,10 +59165,10 @@
         <v>10</v>
       </c>
       <c r="AA440" s="7">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AB440" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC440" s="3" t="s">
         <v>1140</v>
@@ -59186,7 +59186,7 @@
         <v>1144</v>
       </c>
       <c r="AH440" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI440" s="3">
         <v>0</v>
@@ -59195,7 +59195,7 @@
         <v>58</v>
       </c>
       <c r="AK440" s="6">
-        <v>46307.90555991898</v>
+        <v>46301.91933796296</v>
       </c>
       <c r="AL440" s="3" t="s">
         <v>46</v>
@@ -59207,7 +59207,7 @@
         <v>58</v>
       </c>
       <c r="AO440" s="6">
-        <v>46307.90555991898</v>
+        <v>46301.91933796296</v>
       </c>
     </row>
     <row r="441" spans="1:41" x14ac:dyDescent="0.25">
@@ -59236,28 +59236,28 @@
         <v>45</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1154</v>
+        <v>233</v>
       </c>
       <c r="J441" s="3" t="s">
-        <v>1155</v>
+        <v>234</v>
       </c>
       <c r="K441" s="3" t="s">
-        <v>1156</v>
+        <v>235</v>
       </c>
       <c r="L441" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M441" s="3" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="O441" s="3" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="P441" s="3" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="Q441" s="3" t="s">
         <v>46</v>
@@ -59290,10 +59290,10 @@
         <v>10</v>
       </c>
       <c r="AA441" s="7">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="AB441" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC441" s="3" t="s">
         <v>1140</v>
@@ -59311,7 +59311,7 @@
         <v>1144</v>
       </c>
       <c r="AH441" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI441" s="3">
         <v>0</v>
@@ -59361,28 +59361,28 @@
         <v>45</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="J442" s="3" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="K442" s="3" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="L442" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M442" s="3" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="O442" s="3" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="P442" s="3" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="Q442" s="3" t="s">
         <v>46</v>
@@ -59415,7 +59415,7 @@
         <v>10</v>
       </c>
       <c r="AA442" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB442" s="7">
         <v>1</v>
@@ -59748,25 +59748,25 @@
         <v>50</v>
       </c>
       <c r="M445" s="3" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="N445" s="3" t="s">
-        <v>63</v>
+        <v>194</v>
       </c>
       <c r="O445" s="3" t="s">
-        <v>64</v>
+        <v>195</v>
       </c>
       <c r="P445" s="3" t="s">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="Q445" s="5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="R445" s="5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="S445" s="5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="T445" s="3" t="s">
         <v>1139</v>
@@ -59790,7 +59790,7 @@
         <v>46</v>
       </c>
       <c r="AA445" s="7">
-        <v>1147670</v>
+        <v>199584</v>
       </c>
       <c r="AB445" s="7">
         <v>31</v>
@@ -59864,34 +59864,34 @@
         <v>1170</v>
       </c>
       <c r="J446" s="3" t="s">
-        <v>627</v>
+        <v>1171</v>
       </c>
       <c r="K446" s="3" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="L446" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M446" s="3" t="s">
-        <v>207</v>
+        <v>62</v>
       </c>
       <c r="N446" s="3" t="s">
-        <v>208</v>
+        <v>63</v>
       </c>
       <c r="O446" s="3" t="s">
-        <v>209</v>
+        <v>64</v>
       </c>
       <c r="P446" s="3" t="s">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="Q446" s="5">
-        <v>4</v>
-      </c>
-      <c r="R446" s="3">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="R446" s="5">
+        <v>25</v>
       </c>
       <c r="S446" s="5">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T446" s="3" t="s">
         <v>1139</v>
@@ -59915,7 +59915,7 @@
         <v>46</v>
       </c>
       <c r="AA446" s="7">
-        <v>399168</v>
+        <v>1147670</v>
       </c>
       <c r="AB446" s="7">
         <v>31</v>
@@ -59986,37 +59986,37 @@
         <v>1160</v>
       </c>
       <c r="I447" s="3" t="s">
-        <v>1075</v>
+        <v>1173</v>
       </c>
       <c r="J447" s="3" t="s">
-        <v>1076</v>
+        <v>627</v>
       </c>
       <c r="K447" s="3" t="s">
-        <v>1077</v>
+        <v>1174</v>
       </c>
       <c r="L447" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M447" s="3" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="N447" s="3" t="s">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="O447" s="3" t="s">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="P447" s="3" t="s">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="Q447" s="5">
-        <v>12</v>
-      </c>
-      <c r="R447" s="5">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="R447" s="3">
+        <v>0</v>
       </c>
       <c r="S447" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T447" s="3" t="s">
         <v>1139</v>
@@ -60040,7 +60040,7 @@
         <v>46</v>
       </c>
       <c r="AA447" s="7">
-        <v>1133317</v>
+        <v>399168</v>
       </c>
       <c r="AB447" s="7">
         <v>31</v>
@@ -60111,37 +60111,37 @@
         <v>1160</v>
       </c>
       <c r="I448" s="3" t="s">
-        <v>1172</v>
+        <v>1075</v>
       </c>
       <c r="J448" s="3" t="s">
-        <v>1173</v>
+        <v>1076</v>
       </c>
       <c r="K448" s="3" t="s">
-        <v>1174</v>
+        <v>1077</v>
       </c>
       <c r="L448" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M448" s="3" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="N448" s="3" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="O448" s="3" t="s">
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="P448" s="3" t="s">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="Q448" s="5">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="R448" s="5">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="S448" s="5">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="T448" s="3" t="s">
         <v>1139</v>
@@ -60165,7 +60165,7 @@
         <v>46</v>
       </c>
       <c r="AA448" s="7">
-        <v>199584</v>
+        <v>1133317</v>
       </c>
       <c r="AB448" s="7">
         <v>31</v>
@@ -60986,37 +60986,37 @@
         <v>1160</v>
       </c>
       <c r="I455" s="3" t="s">
-        <v>305</v>
+        <v>141</v>
       </c>
       <c r="J455" s="3" t="s">
-        <v>306</v>
+        <v>142</v>
       </c>
       <c r="K455" s="3" t="s">
-        <v>307</v>
+        <v>143</v>
       </c>
       <c r="L455" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M455" s="3" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="N455" s="3" t="s">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="O455" s="3" t="s">
-        <v>163</v>
+        <v>64</v>
       </c>
       <c r="P455" s="3" t="s">
-        <v>164</v>
+        <v>65</v>
       </c>
       <c r="Q455" s="5">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="R455" s="5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S455" s="5">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="T455" s="3" t="s">
         <v>1139</v>
@@ -61040,7 +61040,7 @@
         <v>46</v>
       </c>
       <c r="AA455" s="7">
-        <v>18082468</v>
+        <v>7870700</v>
       </c>
       <c r="AB455" s="7">
         <v>31</v>
@@ -61111,37 +61111,37 @@
         <v>1160</v>
       </c>
       <c r="I456" s="3" t="s">
-        <v>1185</v>
+        <v>170</v>
       </c>
       <c r="J456" s="3" t="s">
-        <v>1186</v>
+        <v>171</v>
       </c>
       <c r="K456" s="3" t="s">
-        <v>560</v>
+        <v>172</v>
       </c>
       <c r="L456" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M456" s="3" t="s">
-        <v>229</v>
+        <v>76</v>
       </c>
       <c r="N456" s="3" t="s">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="O456" s="3" t="s">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="P456" s="3" t="s">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="Q456" s="5">
-        <v>4</v>
-      </c>
-      <c r="R456" s="3">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="R456" s="5">
+        <v>26</v>
       </c>
       <c r="S456" s="5">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="T456" s="3" t="s">
         <v>1139</v>
@@ -61165,7 +61165,7 @@
         <v>46</v>
       </c>
       <c r="AA456" s="7">
-        <v>379200</v>
+        <v>2196976</v>
       </c>
       <c r="AB456" s="7">
         <v>31</v>
@@ -61236,37 +61236,37 @@
         <v>1160</v>
       </c>
       <c r="I457" s="3" t="s">
-        <v>141</v>
+        <v>1185</v>
       </c>
       <c r="J457" s="3" t="s">
-        <v>142</v>
+        <v>1186</v>
       </c>
       <c r="K457" s="3" t="s">
-        <v>143</v>
+        <v>1187</v>
       </c>
       <c r="L457" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M457" s="3" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="N457" s="3" t="s">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="O457" s="3" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="P457" s="3" t="s">
-        <v>65</v>
+        <v>164</v>
       </c>
       <c r="Q457" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R457" s="5">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S457" s="5">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="T457" s="3" t="s">
         <v>1139</v>
@@ -61290,7 +61290,7 @@
         <v>46</v>
       </c>
       <c r="AA457" s="7">
-        <v>7870700</v>
+        <v>1330200</v>
       </c>
       <c r="AB457" s="7">
         <v>31</v>
@@ -61361,37 +61361,37 @@
         <v>1160</v>
       </c>
       <c r="I458" s="3" t="s">
-        <v>170</v>
+        <v>269</v>
       </c>
       <c r="J458" s="3" t="s">
-        <v>171</v>
+        <v>270</v>
       </c>
       <c r="K458" s="3" t="s">
-        <v>172</v>
+        <v>271</v>
       </c>
       <c r="L458" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M458" s="3" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="N458" s="3" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="O458" s="3" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="P458" s="3" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="Q458" s="5">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="R458" s="5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S458" s="5">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="T458" s="3" t="s">
         <v>1139</v>
@@ -61415,7 +61415,7 @@
         <v>46</v>
       </c>
       <c r="AA458" s="7">
-        <v>2196976</v>
+        <v>16986149</v>
       </c>
       <c r="AB458" s="7">
         <v>31</v>
@@ -61486,13 +61486,13 @@
         <v>1160</v>
       </c>
       <c r="I459" s="3" t="s">
-        <v>1187</v>
+        <v>305</v>
       </c>
       <c r="J459" s="3" t="s">
-        <v>1188</v>
+        <v>306</v>
       </c>
       <c r="K459" s="3" t="s">
-        <v>1189</v>
+        <v>307</v>
       </c>
       <c r="L459" s="3" t="s">
         <v>50</v>
@@ -61510,13 +61510,13 @@
         <v>164</v>
       </c>
       <c r="Q459" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R459" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="S459" s="5">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="T459" s="3" t="s">
         <v>1139</v>
@@ -61540,7 +61540,7 @@
         <v>46</v>
       </c>
       <c r="AA459" s="7">
-        <v>1330200</v>
+        <v>18082468</v>
       </c>
       <c r="AB459" s="7">
         <v>31</v>
@@ -61611,37 +61611,37 @@
         <v>1160</v>
       </c>
       <c r="I460" s="3" t="s">
-        <v>269</v>
+        <v>1188</v>
       </c>
       <c r="J460" s="3" t="s">
-        <v>270</v>
+        <v>1189</v>
       </c>
       <c r="K460" s="3" t="s">
-        <v>271</v>
+        <v>560</v>
       </c>
       <c r="L460" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M460" s="3" t="s">
-        <v>137</v>
+        <v>229</v>
       </c>
       <c r="N460" s="3" t="s">
-        <v>138</v>
+        <v>230</v>
       </c>
       <c r="O460" s="3" t="s">
-        <v>139</v>
+        <v>231</v>
       </c>
       <c r="P460" s="3" t="s">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="Q460" s="5">
-        <v>14</v>
-      </c>
-      <c r="R460" s="5">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="R460" s="3">
+        <v>0</v>
       </c>
       <c r="S460" s="5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T460" s="3" t="s">
         <v>1139</v>
@@ -61665,7 +61665,7 @@
         <v>46</v>
       </c>
       <c r="AA460" s="7">
-        <v>16001949</v>
+        <v>379200</v>
       </c>
       <c r="AB460" s="7">
         <v>31</v>
@@ -61861,13 +61861,13 @@
         <v>1160</v>
       </c>
       <c r="I462" s="3" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="J462" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="K462" s="3" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="L462" s="3" t="s">
         <v>50</v>
@@ -62736,37 +62736,37 @@
         <v>1202</v>
       </c>
       <c r="I469" s="3" t="s">
-        <v>1203</v>
+        <v>1164</v>
       </c>
       <c r="J469" s="3" t="s">
-        <v>1204</v>
+        <v>1165</v>
       </c>
       <c r="K469" s="3" t="s">
-        <v>1205</v>
+        <v>1166</v>
       </c>
       <c r="L469" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M469" s="3" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="N469" s="3" t="s">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="O469" s="3" t="s">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="P469" s="3" t="s">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="Q469" s="5">
-        <v>6</v>
-      </c>
-      <c r="R469" s="3">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="R469" s="5">
+        <v>10</v>
       </c>
       <c r="S469" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T469" s="3" t="s">
         <v>1139</v>
@@ -62790,7 +62790,7 @@
         <v>46</v>
       </c>
       <c r="AA469" s="7">
-        <v>2324385</v>
+        <v>848501</v>
       </c>
       <c r="AB469" s="7">
         <v>31</v>
@@ -62861,37 +62861,37 @@
         <v>1202</v>
       </c>
       <c r="I470" s="3" t="s">
-        <v>1164</v>
+        <v>1203</v>
       </c>
       <c r="J470" s="3" t="s">
-        <v>1165</v>
+        <v>1204</v>
       </c>
       <c r="K470" s="3" t="s">
-        <v>1166</v>
+        <v>1205</v>
       </c>
       <c r="L470" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M470" s="3" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="N470" s="3" t="s">
-        <v>208</v>
+        <v>138</v>
       </c>
       <c r="O470" s="3" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="P470" s="3" t="s">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="Q470" s="5">
-        <v>10</v>
-      </c>
-      <c r="R470" s="5">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="R470" s="3">
+        <v>0</v>
       </c>
       <c r="S470" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T470" s="3" t="s">
         <v>1139</v>
@@ -62915,7 +62915,7 @@
         <v>46</v>
       </c>
       <c r="AA470" s="7">
-        <v>848501</v>
+        <v>2324385</v>
       </c>
       <c r="AB470" s="7">
         <v>31</v>
@@ -62986,13 +62986,13 @@
         <v>1160</v>
       </c>
       <c r="I471" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J471" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="K471" s="3" t="s">
         <v>1187</v>
-      </c>
-      <c r="J471" s="3" t="s">
-        <v>1188</v>
-      </c>
-      <c r="K471" s="3" t="s">
-        <v>1189</v>
       </c>
       <c r="L471" s="3" t="s">
         <v>50</v>
@@ -63486,13 +63486,13 @@
         <v>1160</v>
       </c>
       <c r="I475" s="3" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="J475" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="K475" s="3" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="L475" s="3" t="s">
         <v>50</v>
@@ -64915,7 +64915,7 @@
         <v>46</v>
       </c>
       <c r="AA486" s="7">
-        <v>8994825</v>
+        <v>9864825</v>
       </c>
       <c r="AB486" s="7">
         <v>1</v>
@@ -66415,7 +66415,7 @@
         <v>46</v>
       </c>
       <c r="AA498" s="7">
-        <v>471000</v>
+        <v>597118</v>
       </c>
       <c r="AB498" s="7">
         <v>1</v>
@@ -68915,7 +68915,7 @@
         <v>46</v>
       </c>
       <c r="AA518" s="7">
-        <v>710000</v>
+        <v>902000</v>
       </c>
       <c r="AB518" s="7">
         <v>31</v>
@@ -69111,13 +69111,13 @@
         <v>45</v>
       </c>
       <c r="I520" s="3" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="J520" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="K520" s="3" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="L520" s="3" t="s">
         <v>50</v>
@@ -69361,13 +69361,13 @@
         <v>45</v>
       </c>
       <c r="I522" s="3" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="J522" s="3" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="K522" s="3" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="L522" s="3" t="s">
         <v>50</v>
@@ -70885,13 +70885,13 @@
         <v>79</v>
       </c>
       <c r="Q534" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R534" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S534" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T534" s="3" t="s">
         <v>1139</v>
@@ -71361,13 +71361,13 @@
         <v>1160</v>
       </c>
       <c r="I538" s="3" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="J538" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="K538" s="3" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="L538" s="3" t="s">
         <v>50</v>
@@ -71611,37 +71611,37 @@
         <v>1160</v>
       </c>
       <c r="I540" s="3" t="s">
-        <v>638</v>
+        <v>1052</v>
       </c>
       <c r="J540" s="3" t="s">
-        <v>639</v>
+        <v>1053</v>
       </c>
       <c r="K540" s="3" t="s">
-        <v>640</v>
+        <v>1054</v>
       </c>
       <c r="L540" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M540" s="3" t="s">
-        <v>147</v>
+        <v>62</v>
       </c>
       <c r="N540" s="3" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="O540" s="3" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="P540" s="3" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="Q540" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="R540" s="5">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S540" s="5">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T540" s="3" t="s">
         <v>1139</v>
@@ -71665,7 +71665,7 @@
         <v>46</v>
       </c>
       <c r="AA540" s="7">
-        <v>2734208</v>
+        <v>672100</v>
       </c>
       <c r="AB540" s="7">
         <v>31</v>
@@ -71736,37 +71736,37 @@
         <v>1160</v>
       </c>
       <c r="I541" s="3" t="s">
-        <v>1277</v>
+        <v>638</v>
       </c>
       <c r="J541" s="3" t="s">
-        <v>1278</v>
+        <v>639</v>
       </c>
       <c r="K541" s="3" t="s">
-        <v>1279</v>
+        <v>640</v>
       </c>
       <c r="L541" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M541" s="3" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="N541" s="3" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="O541" s="3" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="P541" s="3" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="Q541" s="5">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="R541" s="5">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="S541" s="5">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="T541" s="3" t="s">
         <v>1139</v>
@@ -71790,7 +71790,7 @@
         <v>46</v>
       </c>
       <c r="AA541" s="7">
-        <v>1880508</v>
+        <v>2734208</v>
       </c>
       <c r="AB541" s="7">
         <v>31</v>
@@ -71861,37 +71861,37 @@
         <v>1160</v>
       </c>
       <c r="I542" s="3" t="s">
-        <v>660</v>
+        <v>1277</v>
       </c>
       <c r="J542" s="3" t="s">
-        <v>661</v>
+        <v>1278</v>
       </c>
       <c r="K542" s="3" t="s">
-        <v>662</v>
+        <v>1279</v>
       </c>
       <c r="L542" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M542" s="3" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="N542" s="3" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="O542" s="3" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="P542" s="3" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="Q542" s="5">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="R542" s="5">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="S542" s="5">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="T542" s="3" t="s">
         <v>1139</v>
@@ -71915,7 +71915,7 @@
         <v>46</v>
       </c>
       <c r="AA542" s="7">
-        <v>1218465</v>
+        <v>1880508</v>
       </c>
       <c r="AB542" s="7">
         <v>31</v>
@@ -71986,34 +71986,34 @@
         <v>1160</v>
       </c>
       <c r="I543" s="3" t="s">
-        <v>684</v>
+        <v>660</v>
       </c>
       <c r="J543" s="3" t="s">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="K543" s="3" t="s">
-        <v>686</v>
+        <v>662</v>
       </c>
       <c r="L543" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M543" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="N543" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="O543" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="P543" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q543" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R543" s="5">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S543" s="5">
         <v>13</v>
@@ -72039,8 +72039,8 @@
       <c r="Z543" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA543" s="3" t="s">
-        <v>46</v>
+      <c r="AA543" s="7">
+        <v>1218465</v>
       </c>
       <c r="AB543" s="7">
         <v>31</v>
@@ -72111,37 +72111,37 @@
         <v>1160</v>
       </c>
       <c r="I544" s="3" t="s">
-        <v>1199</v>
+        <v>684</v>
       </c>
       <c r="J544" s="3" t="s">
-        <v>1200</v>
+        <v>685</v>
       </c>
       <c r="K544" s="3" t="s">
-        <v>1201</v>
+        <v>686</v>
       </c>
       <c r="L544" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M544" s="3" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="N544" s="3" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="O544" s="3" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="P544" s="3" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="Q544" s="5">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="R544" s="5">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="S544" s="5">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="T544" s="3" t="s">
         <v>1139</v>
@@ -72164,8 +72164,8 @@
       <c r="Z544" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA544" s="7">
-        <v>1507880</v>
+      <c r="AA544" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB544" s="7">
         <v>31</v>
@@ -72236,37 +72236,37 @@
         <v>1160</v>
       </c>
       <c r="I545" s="3" t="s">
-        <v>1052</v>
+        <v>1199</v>
       </c>
       <c r="J545" s="3" t="s">
-        <v>1053</v>
+        <v>1200</v>
       </c>
       <c r="K545" s="3" t="s">
-        <v>1054</v>
+        <v>1201</v>
       </c>
       <c r="L545" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M545" s="3" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="N545" s="3" t="s">
-        <v>63</v>
+        <v>194</v>
       </c>
       <c r="O545" s="3" t="s">
-        <v>64</v>
+        <v>195</v>
       </c>
       <c r="P545" s="3" t="s">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="Q545" s="5">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="R545" s="5">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="S545" s="5">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="T545" s="3" t="s">
         <v>1139</v>
@@ -72290,7 +72290,7 @@
         <v>46</v>
       </c>
       <c r="AA545" s="7">
-        <v>672100</v>
+        <v>1507880</v>
       </c>
       <c r="AB545" s="7">
         <v>31</v>
@@ -72361,37 +72361,37 @@
         <v>1287</v>
       </c>
       <c r="I546" s="3" t="s">
-        <v>614</v>
+        <v>1075</v>
       </c>
       <c r="J546" s="3" t="s">
-        <v>615</v>
+        <v>1076</v>
       </c>
       <c r="K546" s="3" t="s">
-        <v>616</v>
+        <v>1077</v>
       </c>
       <c r="L546" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M546" s="3" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="N546" s="3" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="O546" s="3" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="P546" s="3" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="Q546" s="5">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="R546" s="5">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="S546" s="5">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="T546" s="3" t="s">
         <v>1139</v>
@@ -72415,7 +72415,7 @@
         <v>46</v>
       </c>
       <c r="AA546" s="7">
-        <v>3741248</v>
+        <v>4678207</v>
       </c>
       <c r="AB546" s="7">
         <v>31</v>
@@ -72486,37 +72486,37 @@
         <v>1287</v>
       </c>
       <c r="I547" s="3" t="s">
-        <v>1075</v>
+        <v>614</v>
       </c>
       <c r="J547" s="3" t="s">
-        <v>1076</v>
+        <v>615</v>
       </c>
       <c r="K547" s="3" t="s">
-        <v>1077</v>
+        <v>616</v>
       </c>
       <c r="L547" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M547" s="3" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="N547" s="3" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="O547" s="3" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="P547" s="3" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="Q547" s="5">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="R547" s="5">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="S547" s="5">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="T547" s="3" t="s">
         <v>1139</v>
@@ -72540,7 +72540,7 @@
         <v>46</v>
       </c>
       <c r="AA547" s="7">
-        <v>4678207</v>
+        <v>3741248</v>
       </c>
       <c r="AB547" s="7">
         <v>31</v>
@@ -75111,13 +75111,13 @@
         <v>45</v>
       </c>
       <c r="I568" s="3" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="J568" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="K568" s="3" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="L568" s="3" t="s">
         <v>50</v>
@@ -75665,7 +75665,7 @@
         <v>46</v>
       </c>
       <c r="AA572" s="7">
-        <v>1407238</v>
+        <v>1867238</v>
       </c>
       <c r="AB572" s="7">
         <v>31</v>
@@ -76415,7 +76415,7 @@
         <v>46</v>
       </c>
       <c r="AA578" s="7">
-        <v>3163624</v>
+        <v>5198074</v>
       </c>
       <c r="AB578" s="7">
         <v>31</v>
@@ -77289,8 +77289,8 @@
       <c r="Z585" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA585" s="3" t="s">
-        <v>46</v>
+      <c r="AA585" s="7">
+        <v>156000</v>
       </c>
       <c r="AB585" s="7">
         <v>31</v>
@@ -77540,7 +77540,7 @@
         <v>46</v>
       </c>
       <c r="AA587" s="7">
-        <v>455000</v>
+        <v>762981</v>
       </c>
       <c r="AB587" s="7">
         <v>31</v>
